--- a/data/general.xlsx
+++ b/data/general.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/04 Abril/Dasboatdde marzo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/05 Mayo/Dasboatdde abril/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530565D9-7F75-4E4C-9F2E-CE9581CC78F3}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97466149-1552-4EBF-8B28-94E07997FF45}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F008453E-1A06-40CE-9AA2-8079F823278A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>CVS</t>
   </si>
@@ -68,73 +68,76 @@
     <t>Accesorios</t>
   </si>
   <si>
-    <t>BARBOSA</t>
-  </si>
-  <si>
-    <t>CAUCASIA</t>
-  </si>
-  <si>
-    <t>CIUDAD BOLIVAR</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>DABEIBA</t>
-  </si>
-  <si>
-    <t>CALDAS</t>
-  </si>
-  <si>
-    <t>DON MATIAS</t>
-  </si>
-  <si>
-    <t>EL BAGRE</t>
-  </si>
-  <si>
-    <t>FRONTINO</t>
-  </si>
-  <si>
-    <t>COPACABANA</t>
-  </si>
-  <si>
-    <t>GIRARDOTA</t>
-  </si>
-  <si>
-    <t>LA ESTRELLA</t>
-  </si>
-  <si>
-    <t>NECHI</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>ENVIGADO</t>
-  </si>
-  <si>
-    <t>SEGOVIA</t>
-  </si>
-  <si>
-    <t>YARUMAL</t>
-  </si>
-  <si>
-    <t>ZARAGOZA</t>
-  </si>
-  <si>
-    <t>ITAGUI</t>
-  </si>
-  <si>
-    <t>JUNIN</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>TERMINAL NORTE</t>
-  </si>
-  <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Barbosa</t>
+  </si>
+  <si>
+    <t>Bello</t>
+  </si>
+  <si>
+    <t>Caldas</t>
+  </si>
+  <si>
+    <t>Caucasia</t>
+  </si>
+  <si>
+    <t>Ciudad Bolivar</t>
+  </si>
+  <si>
+    <t>Copacabana</t>
+  </si>
+  <si>
+    <t>Dabeiba</t>
+  </si>
+  <si>
+    <t>Don Matias</t>
+  </si>
+  <si>
+    <t>El Bagre</t>
+  </si>
+  <si>
+    <t>Envigado</t>
+  </si>
+  <si>
+    <t>Frontino</t>
+  </si>
+  <si>
+    <t>Girardota</t>
+  </si>
+  <si>
+    <t>Itagui</t>
+  </si>
+  <si>
+    <t>Junin</t>
+  </si>
+  <si>
+    <t>La Estrella</t>
+  </si>
+  <si>
+    <t>Nechi</t>
+  </si>
+  <si>
+    <t>Prado</t>
+  </si>
+  <si>
+    <t>Sabaneta</t>
+  </si>
+  <si>
+    <t>Segovia</t>
+  </si>
+  <si>
+    <t>Terminal Norte</t>
+  </si>
+  <si>
+    <t>Yarumal</t>
+  </si>
+  <si>
+    <t>Zaragoza</t>
+  </si>
+  <si>
+    <t>San Cristobal</t>
   </si>
 </sst>
 </file>
@@ -245,7 +248,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -317,6 +320,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -657,13 +663,12 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="3" max="4" width="12.140625" style="23" customWidth="1"/>
     <col min="5" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="10" width="13.42578125" customWidth="1"/>
@@ -748,211 +753,206 @@
     </row>
     <row r="2" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="16">
         <v>2400</v>
       </c>
-      <c r="C2">
-        <v>2666.0699999999993</v>
+      <c r="C2" s="26">
+        <v>2116.2600000000002</v>
       </c>
       <c r="D2" s="18">
-        <v>1.1108624999999996</v>
+        <v>0.88177500000000009</v>
       </c>
       <c r="E2" s="16">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F2" s="16">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G2" s="18">
-        <v>0.89189189189189189</v>
+        <v>0.7</v>
       </c>
       <c r="H2" s="17">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I2" s="17">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J2" s="18">
-        <v>0.90243902439024393</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="K2" s="16">
+        <v>8</v>
+      </c>
+      <c r="L2" s="16">
         <v>6</v>
       </c>
-      <c r="L2" s="16">
-        <v>11</v>
-      </c>
       <c r="M2" s="18">
-        <v>1.8333333333333333</v>
-      </c>
-      <c r="N2" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="N2">
         <v>1500</v>
       </c>
       <c r="O2" s="16">
-        <v>1170</v>
+        <v>1485</v>
       </c>
       <c r="P2" s="18">
-        <f>O2/N2</f>
-        <v>0.78</v>
-      </c>
-      <c r="Q2" s="16">
-        <v>95</v>
+        <v>0.99</v>
+      </c>
+      <c r="Q2">
+        <v>72</v>
       </c>
       <c r="R2" s="16">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="S2" s="18">
-        <v>1.1578947368421053</v>
+        <v>1.3611111111111112</v>
       </c>
       <c r="T2" s="24">
-        <v>9500000</v>
+        <v>8000000</v>
       </c>
       <c r="U2" s="24">
-        <v>7033084</v>
+        <v>7969000</v>
       </c>
       <c r="V2" s="19">
-        <f>U2/T2</f>
-        <v>0.74032463157894735</v>
+        <v>0.99612500000000004</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="16">
         <v>2850</v>
       </c>
-      <c r="C3">
-        <v>2526.659999999998</v>
+      <c r="C3" s="26">
+        <v>2611.2200000000007</v>
       </c>
       <c r="D3" s="18">
-        <v>0.88654736842105197</v>
+        <v>0.91621754385964937</v>
       </c>
       <c r="E3" s="16">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F3" s="16">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="G3" s="18">
-        <v>0.84615384615384615</v>
+        <v>1.34</v>
       </c>
       <c r="H3" s="17">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I3" s="17">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="J3" s="18">
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="K3" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L3" s="16">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M3" s="18">
-        <v>1.7</v>
-      </c>
-      <c r="N3" s="16">
-        <v>0</v>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="N3">
+        <v>1500</v>
       </c>
       <c r="O3" s="16">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="P3" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="16">
-        <v>32</v>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="Q3">
+        <v>150</v>
       </c>
       <c r="R3" s="16">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="S3" s="18">
-        <v>0.65625</v>
+        <v>1.08</v>
       </c>
       <c r="T3" s="24">
-        <v>5500000</v>
+        <v>4000000</v>
       </c>
       <c r="U3" s="24">
-        <v>1707900</v>
+        <v>5182656</v>
       </c>
       <c r="V3" s="19">
-        <f t="shared" ref="V3:V24" si="0">U3/T3</f>
-        <v>0.31052727272727271</v>
+        <v>1.2956639999999999</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="16">
         <v>3500</v>
       </c>
-      <c r="C4">
-        <v>3744.9599999999996</v>
+      <c r="C4" s="26">
+        <v>3541.9900000000043</v>
       </c>
       <c r="D4" s="18">
-        <v>1.0699885714285713</v>
+        <v>1.0119971428571441</v>
       </c>
       <c r="E4" s="16">
         <v>62</v>
       </c>
       <c r="F4" s="16">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G4" s="18">
-        <v>1.1935483870967742</v>
+        <v>1.3870967741935485</v>
       </c>
       <c r="H4" s="17">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="I4" s="17">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="J4" s="18">
-        <v>0.90769230769230769</v>
+        <v>1.0166666666666666</v>
       </c>
       <c r="K4" s="16">
         <v>10</v>
       </c>
       <c r="L4" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M4" s="18">
-        <v>1.2</v>
-      </c>
-      <c r="N4" s="16">
-        <v>800</v>
+        <v>0.8</v>
+      </c>
+      <c r="N4">
+        <v>1500</v>
       </c>
       <c r="O4" s="16">
-        <v>865</v>
+        <v>1531</v>
       </c>
       <c r="P4" s="18">
-        <f t="shared" ref="P4:P24" si="1">O4/N4</f>
-        <v>1.08125</v>
-      </c>
-      <c r="Q4" s="16">
-        <v>135</v>
+        <v>1.0206666666666666</v>
+      </c>
+      <c r="Q4">
+        <v>210</v>
       </c>
       <c r="R4" s="16">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="S4" s="18">
-        <v>1.0666666666666667</v>
+        <v>1.1952380952380952</v>
       </c>
       <c r="T4" s="24">
-        <v>12000000</v>
+        <v>9000000</v>
       </c>
       <c r="U4" s="24">
-        <v>4067000</v>
+        <v>9074900</v>
       </c>
       <c r="V4" s="19">
-        <f t="shared" si="0"/>
-        <v>0.33891666666666664</v>
+        <v>1.0083222222222221</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
@@ -962,29 +962,29 @@
       <c r="B5" s="16">
         <v>1350</v>
       </c>
-      <c r="C5">
-        <v>672.53000000000009</v>
+      <c r="C5" s="26">
+        <v>951.13999999999987</v>
       </c>
       <c r="D5" s="18">
-        <v>0.49817037037037043</v>
+        <v>0.70454814814814803</v>
       </c>
       <c r="E5" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" s="18">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="17">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I5" s="17">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J5" s="18">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
       <c r="K5" s="16">
         <v>4</v>
@@ -995,206 +995,200 @@
       <c r="M5" s="18">
         <v>0</v>
       </c>
-      <c r="N5" s="16">
-        <v>1200</v>
+      <c r="N5">
+        <v>0</v>
       </c>
       <c r="O5" s="16">
-        <v>936</v>
+        <v>0</v>
       </c>
       <c r="P5" s="18">
-        <f t="shared" si="1"/>
-        <v>0.78</v>
-      </c>
-      <c r="Q5" s="16">
-        <v>69</v>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>20</v>
       </c>
       <c r="R5" s="16">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="S5" s="18">
-        <v>1.2173913043478262</v>
+        <v>1</v>
       </c>
       <c r="T5" s="24">
-        <v>4000000</v>
+        <v>2500000</v>
       </c>
       <c r="U5" s="24">
-        <v>3017000</v>
+        <v>1650000</v>
       </c>
       <c r="V5" s="19">
-        <f t="shared" si="0"/>
-        <v>0.75424999999999998</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="16">
-        <v>1700</v>
-      </c>
-      <c r="C6">
-        <v>1473.0499999999997</v>
+        <v>1500</v>
+      </c>
+      <c r="C6" s="26">
+        <v>1163.1599999999999</v>
       </c>
       <c r="D6" s="18">
-        <v>0.86649999999999983</v>
+        <v>0.77543999999999991</v>
       </c>
       <c r="E6" s="16">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F6" s="16">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G6" s="18">
-        <v>0.54545454545454541</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="17">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I6" s="17">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J6" s="18">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="K6" s="16">
         <v>1</v>
       </c>
       <c r="L6" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="18">
-        <v>2</v>
-      </c>
-      <c r="N6" s="16">
-        <v>1200</v>
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>800</v>
       </c>
       <c r="O6" s="16">
-        <v>1156</v>
+        <v>971</v>
       </c>
       <c r="P6" s="18">
-        <f t="shared" si="1"/>
-        <v>0.96333333333333337</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>68</v>
+        <v>1.2137500000000001</v>
+      </c>
+      <c r="Q6">
+        <v>135</v>
       </c>
       <c r="R6" s="16">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="S6" s="18">
-        <v>1.2352941176470589</v>
+        <v>0.68888888888888888</v>
       </c>
       <c r="T6" s="24">
-        <v>6000000</v>
+        <v>4500000</v>
       </c>
       <c r="U6" s="24">
-        <v>5744606</v>
+        <v>4522000</v>
       </c>
       <c r="V6" s="19">
-        <f t="shared" si="0"/>
-        <v>0.95743433333333339</v>
+        <v>1.0048888888888889</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="16">
         <v>2800</v>
       </c>
-      <c r="C7">
-        <v>3858.6099999999979</v>
+      <c r="C7" s="26">
+        <v>2714.5999999999985</v>
       </c>
       <c r="D7" s="18">
-        <v>1.3780749999999993</v>
+        <v>0.96949999999999947</v>
       </c>
       <c r="E7" s="16">
         <v>47</v>
       </c>
       <c r="F7" s="16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G7" s="18">
-        <v>1.1702127659574468</v>
+        <v>1.2765957446808511</v>
       </c>
       <c r="H7" s="17">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="I7" s="17">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="J7" s="18">
-        <v>0.71250000000000002</v>
+        <v>0.68421052631578949</v>
       </c>
       <c r="K7" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L7" s="16">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M7" s="18">
-        <v>1.7</v>
-      </c>
-      <c r="N7" s="16">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="N7">
         <v>1500</v>
       </c>
       <c r="O7" s="16">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="P7" s="18">
-        <f t="shared" si="1"/>
-        <v>0.94866666666666666</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>176</v>
+        <v>0.95066666666666666</v>
+      </c>
+      <c r="Q7">
+        <v>180</v>
       </c>
       <c r="R7" s="16">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="S7" s="18">
-        <v>1.0852272727272727</v>
+        <v>0.91111111111111109</v>
       </c>
       <c r="T7" s="24">
-        <v>11000000</v>
+        <v>8500000</v>
       </c>
       <c r="U7" s="24">
-        <v>7699000</v>
+        <v>8656900</v>
       </c>
       <c r="V7" s="19">
-        <f t="shared" si="0"/>
-        <v>0.69990909090909093</v>
+        <v>1.0184588235294119</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="16">
         <v>1450</v>
       </c>
-      <c r="C8">
-        <v>1512.6199999999997</v>
+      <c r="C8" s="26">
+        <v>909.41999999999973</v>
       </c>
       <c r="D8" s="18">
-        <v>1.0431862068965514</v>
+        <v>0.62718620689655158</v>
       </c>
       <c r="E8" s="16">
         <v>18</v>
       </c>
       <c r="F8" s="16">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G8" s="18">
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H8" s="17">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="I8" s="17">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="J8" s="18">
-        <v>0.75714285714285712</v>
+        <v>0.64</v>
       </c>
       <c r="K8" s="16">
         <v>1</v>
@@ -1205,48 +1199,46 @@
       <c r="M8" s="18">
         <v>0</v>
       </c>
-      <c r="N8" s="16">
-        <v>1500</v>
+      <c r="N8">
+        <v>1200</v>
       </c>
       <c r="O8" s="16">
-        <v>578</v>
+        <v>1206</v>
       </c>
       <c r="P8" s="18">
-        <f t="shared" si="1"/>
-        <v>0.38533333333333336</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>98</v>
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="Q8">
+        <v>75</v>
       </c>
       <c r="R8" s="16">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S8" s="18">
-        <v>0.7142857142857143</v>
+        <v>0.8</v>
       </c>
       <c r="T8" s="24">
-        <v>3000000</v>
+        <v>2500000</v>
       </c>
       <c r="U8" s="24">
-        <v>6847000</v>
+        <v>1705000</v>
       </c>
       <c r="V8" s="19">
-        <f t="shared" si="0"/>
-        <v>2.2823333333333333</v>
+        <v>0.68200000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="16">
         <v>1500</v>
       </c>
-      <c r="C9">
-        <v>1596.4099999999989</v>
+      <c r="C9" s="26">
+        <v>1455.4999999999998</v>
       </c>
       <c r="D9" s="18">
-        <v>1.0642733333333327</v>
+        <v>0.97033333333333316</v>
       </c>
       <c r="E9" s="16">
         <v>37</v>
@@ -1258,223 +1250,217 @@
         <v>1.027027027027027</v>
       </c>
       <c r="H9" s="17">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="I9" s="17">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="J9" s="18">
-        <v>0.9107142857142857</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="K9" s="16">
         <v>1</v>
       </c>
       <c r="L9" s="16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="18">
-        <v>2</v>
-      </c>
-      <c r="N9" s="16">
+        <v>0</v>
+      </c>
+      <c r="N9">
         <v>1200</v>
       </c>
       <c r="O9" s="16">
-        <v>1202</v>
+        <v>1104</v>
       </c>
       <c r="P9" s="18">
-        <f t="shared" si="1"/>
-        <v>1.0016666666666667</v>
-      </c>
-      <c r="Q9" s="16">
-        <v>128</v>
+        <v>0.92</v>
+      </c>
+      <c r="Q9">
+        <v>80</v>
       </c>
       <c r="R9" s="16">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="S9" s="18">
-        <v>1.1484375</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="T9" s="24">
-        <v>5500000</v>
+        <v>4500000</v>
       </c>
       <c r="U9" s="24">
-        <v>4847900</v>
+        <v>5751900</v>
       </c>
       <c r="V9" s="19">
-        <f t="shared" si="0"/>
-        <v>0.88143636363636368</v>
+        <v>1.2782</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="16">
         <v>4000</v>
       </c>
-      <c r="C10">
-        <v>3183.61</v>
+      <c r="C10" s="26">
+        <v>2874.1300000000024</v>
       </c>
       <c r="D10" s="18">
-        <v>0.79590250000000007</v>
+        <v>0.71853250000000057</v>
       </c>
       <c r="E10" s="16">
         <v>42</v>
       </c>
       <c r="F10" s="16">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G10" s="18">
-        <v>1.5714285714285714</v>
+        <v>1.1904761904761905</v>
       </c>
       <c r="H10" s="17">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="I10" s="17">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="J10" s="18">
-        <v>0.84</v>
+        <v>0.86153846153846159</v>
       </c>
       <c r="K10" s="16">
         <v>1</v>
       </c>
       <c r="L10" s="16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" s="18">
-        <v>4</v>
-      </c>
-      <c r="N10" s="16">
-        <v>1200</v>
+        <v>3</v>
+      </c>
+      <c r="N10">
+        <v>1500</v>
       </c>
       <c r="O10" s="16">
-        <v>964</v>
+        <v>1529</v>
       </c>
       <c r="P10" s="18">
-        <f t="shared" si="1"/>
-        <v>0.80333333333333334</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>54</v>
+        <v>1.0193333333333334</v>
+      </c>
+      <c r="Q10">
+        <v>180</v>
       </c>
       <c r="R10" s="16">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="S10" s="18">
-        <v>1.4259259259259258</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="T10" s="24">
-        <v>10000000</v>
+        <v>8500000</v>
       </c>
       <c r="U10" s="24">
-        <v>947000</v>
+        <v>6566800</v>
       </c>
       <c r="V10" s="19">
-        <f t="shared" si="0"/>
-        <v>9.4700000000000006E-2</v>
+        <v>0.77256470588235293</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="16">
         <v>3500</v>
       </c>
-      <c r="C11">
-        <v>3098.2899999999986</v>
+      <c r="C11" s="26">
+        <v>3166.6600000000026</v>
       </c>
       <c r="D11" s="18">
-        <v>0.88522571428571384</v>
+        <v>0.90476000000000079</v>
       </c>
       <c r="E11" s="16">
         <v>78</v>
       </c>
       <c r="F11" s="16">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G11" s="18">
-        <v>0.94871794871794868</v>
+        <v>1.0512820512820513</v>
       </c>
       <c r="H11" s="17">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I11" s="17">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="J11" s="18">
-        <v>0.79268292682926833</v>
+        <v>0.95294117647058818</v>
       </c>
       <c r="K11" s="16">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L11" s="16">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M11" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="N11" s="16">
-        <v>800</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N11">
+        <v>1500</v>
       </c>
       <c r="O11" s="16">
-        <v>553</v>
+        <v>1354</v>
       </c>
       <c r="P11" s="18">
-        <f t="shared" si="1"/>
-        <v>0.69125000000000003</v>
-      </c>
-      <c r="Q11" s="16">
-        <v>60</v>
+        <v>0.90266666666666662</v>
+      </c>
+      <c r="Q11">
+        <v>190</v>
       </c>
       <c r="R11" s="16">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="S11" s="18">
-        <v>1.2</v>
+        <v>1.0315789473684212</v>
       </c>
       <c r="T11" s="24">
         <v>4000000</v>
       </c>
       <c r="U11" s="24">
-        <v>3478000</v>
+        <v>3041000</v>
       </c>
       <c r="V11" s="19">
-        <f t="shared" si="0"/>
-        <v>0.86950000000000005</v>
+        <v>0.76024999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" s="16">
-        <v>2600</v>
-      </c>
-      <c r="C12">
-        <v>2256.5700000000002</v>
+        <v>2400</v>
+      </c>
+      <c r="C12" s="26">
+        <v>2408.8700000000003</v>
       </c>
       <c r="D12" s="18">
-        <v>0.86791153846153857</v>
+        <v>1.0036958333333335</v>
       </c>
       <c r="E12" s="16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F12" s="16">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G12" s="18">
-        <v>0.92307692307692313</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="H12" s="17">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="I12" s="17">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="J12" s="18">
-        <v>1.2</v>
+        <v>1.0545454545454545</v>
       </c>
       <c r="K12" s="16">
         <v>1</v>
@@ -1485,594 +1471,576 @@
       <c r="M12" s="18">
         <v>0</v>
       </c>
-      <c r="N12" s="16">
-        <v>1200</v>
+      <c r="N12">
+        <v>1500</v>
       </c>
       <c r="O12" s="16">
-        <v>317</v>
+        <v>641</v>
       </c>
       <c r="P12" s="18">
-        <f t="shared" si="1"/>
-        <v>0.26416666666666666</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>74</v>
+        <v>0.42733333333333334</v>
+      </c>
+      <c r="Q12">
+        <v>90</v>
       </c>
       <c r="R12" s="16">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="S12" s="18">
-        <v>0.97297297297297303</v>
+        <v>0.68888888888888888</v>
       </c>
       <c r="T12" s="24">
-        <v>12000000</v>
+        <v>7000000</v>
       </c>
       <c r="U12" s="24">
-        <v>928000</v>
+        <v>8405900</v>
       </c>
       <c r="V12" s="19">
-        <f t="shared" si="0"/>
-        <v>7.7333333333333337E-2</v>
+        <v>1.2008428571428571</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B13" s="16">
         <v>2000</v>
       </c>
-      <c r="C13">
-        <v>1984.9700000000003</v>
+      <c r="C13" s="26">
+        <v>1616.3200000000004</v>
       </c>
       <c r="D13" s="18">
-        <v>0.99248500000000017</v>
+        <v>0.80816000000000021</v>
       </c>
       <c r="E13" s="16">
         <v>32</v>
       </c>
       <c r="F13" s="16">
+        <v>39</v>
+      </c>
+      <c r="G13" s="18">
+        <v>1.21875</v>
+      </c>
+      <c r="H13" s="17">
+        <v>50</v>
+      </c>
+      <c r="I13" s="17">
         <v>38</v>
       </c>
-      <c r="G13" s="18">
-        <v>1.1875</v>
-      </c>
-      <c r="H13" s="17">
-        <v>60</v>
-      </c>
-      <c r="I13" s="17">
-        <v>51</v>
-      </c>
       <c r="J13" s="18">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="K13" s="16">
         <v>6</v>
       </c>
       <c r="L13" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M13" s="18">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N13" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="N13">
         <v>1200</v>
       </c>
       <c r="O13" s="16">
-        <v>1029</v>
+        <v>1215</v>
       </c>
       <c r="P13" s="18">
-        <f t="shared" si="1"/>
-        <v>0.85750000000000004</v>
-      </c>
-      <c r="Q13" s="16">
-        <v>183</v>
+        <v>1.0125</v>
+      </c>
+      <c r="Q13">
+        <v>130</v>
       </c>
       <c r="R13" s="16">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="S13" s="18">
-        <v>1.46448087431694</v>
+        <v>1.0846153846153845</v>
       </c>
       <c r="T13" s="24">
-        <v>5500000</v>
+        <v>4500000</v>
       </c>
       <c r="U13" s="24">
-        <v>4954000</v>
+        <v>4480000</v>
       </c>
       <c r="V13" s="19">
-        <f t="shared" si="0"/>
-        <v>0.90072727272727271</v>
+        <v>0.99555555555555553</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B14" s="16">
         <v>2300</v>
       </c>
-      <c r="C14">
-        <v>2336.46</v>
+      <c r="C14" s="26">
+        <v>2772.5900000000011</v>
       </c>
       <c r="D14" s="18">
-        <v>1.0158521739130435</v>
+        <v>1.2054739130434786</v>
       </c>
       <c r="E14" s="16">
         <v>44</v>
       </c>
       <c r="F14" s="16">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G14" s="18">
-        <v>1.1363636363636365</v>
+        <v>1.75</v>
       </c>
       <c r="H14" s="17">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I14" s="17">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="J14" s="18">
-        <v>0.6333333333333333</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K14" s="16">
         <v>10</v>
       </c>
       <c r="L14" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M14" s="18">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="N14" s="16">
-        <v>1200</v>
+        <v>1.2</v>
+      </c>
+      <c r="N14">
+        <v>1500</v>
       </c>
       <c r="O14" s="16">
-        <v>1074</v>
+        <v>1544</v>
       </c>
       <c r="P14" s="18">
-        <f t="shared" si="1"/>
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>168</v>
+        <v>1.0293333333333334</v>
+      </c>
+      <c r="Q14">
+        <v>160</v>
       </c>
       <c r="R14" s="16">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="S14" s="18">
-        <v>1.0059523809523809</v>
+        <v>1.25</v>
       </c>
       <c r="T14" s="24">
-        <v>4000000</v>
+        <v>3500000</v>
       </c>
       <c r="U14" s="24">
-        <v>2014000</v>
+        <v>1009000</v>
       </c>
       <c r="V14" s="19">
-        <f t="shared" si="0"/>
-        <v>0.50349999999999995</v>
+        <v>0.28828571428571431</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B15" s="16">
         <v>6000</v>
       </c>
-      <c r="C15">
-        <v>7187.6800000000139</v>
+      <c r="C15" s="26">
+        <v>6399.6500000000115</v>
       </c>
       <c r="D15" s="18">
-        <v>1.1979466666666689</v>
+        <v>1.0666083333333352</v>
       </c>
       <c r="E15" s="16">
         <v>103</v>
       </c>
       <c r="F15" s="16">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="G15" s="18">
-        <v>1.7475728155339805</v>
+        <v>1.4077669902912622</v>
       </c>
       <c r="H15" s="17">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="I15" s="17">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="J15" s="18">
-        <v>1.0138888888888888</v>
+        <v>0.90454545454545454</v>
       </c>
       <c r="K15" s="16">
         <v>14</v>
       </c>
       <c r="L15" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M15" s="18">
-        <v>1.0714285714285714</v>
-      </c>
-      <c r="N15" s="16">
-        <v>1200</v>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="N15">
+        <v>1500</v>
       </c>
       <c r="O15" s="16">
-        <v>1014</v>
+        <v>520</v>
       </c>
       <c r="P15" s="18">
-        <f t="shared" si="1"/>
-        <v>0.84499999999999997</v>
-      </c>
-      <c r="Q15" s="16">
-        <v>92</v>
+        <v>0.34666666666666668</v>
+      </c>
+      <c r="Q15">
+        <v>400</v>
       </c>
       <c r="R15" s="16">
-        <v>96</v>
+        <v>517</v>
       </c>
       <c r="S15" s="18">
-        <v>1.0434782608695652</v>
+        <v>1.2925</v>
       </c>
       <c r="T15" s="24">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
       <c r="U15" s="24">
-        <v>6813000</v>
+        <v>5763000</v>
       </c>
       <c r="V15" s="19">
-        <f t="shared" si="0"/>
-        <v>0.97328571428571431</v>
+        <v>0.96050000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B16" s="16">
         <v>1500</v>
       </c>
-      <c r="C16">
-        <v>869.86</v>
+      <c r="C16" s="26">
+        <v>963.89000000000033</v>
       </c>
       <c r="D16" s="18">
-        <v>0.57990666666666668</v>
+        <v>0.64259333333333357</v>
       </c>
       <c r="E16" s="16">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" s="16">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" s="18">
-        <v>0.76470588235294112</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="H16" s="17">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="I16" s="17">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="J16" s="18">
-        <v>0.81372549019607843</v>
+        <v>1.08</v>
       </c>
       <c r="K16" s="16">
         <v>6</v>
       </c>
       <c r="L16" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M16" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="N16" s="16">
-        <v>1500</v>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="N16">
+        <v>1200</v>
       </c>
       <c r="O16" s="16">
-        <v>1730</v>
+        <v>1091</v>
       </c>
       <c r="P16" s="18">
-        <f t="shared" si="1"/>
-        <v>1.1533333333333333</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>129</v>
+        <v>0.90916666666666668</v>
+      </c>
+      <c r="Q16">
+        <v>65</v>
       </c>
       <c r="R16" s="16">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="S16" s="18">
-        <v>1.4341085271317831</v>
+        <v>0.89230769230769236</v>
       </c>
       <c r="T16" s="24">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="U16" s="24">
-        <v>4368000</v>
+        <v>1996000</v>
       </c>
       <c r="V16" s="19">
-        <f t="shared" si="0"/>
-        <v>1.456</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B17" s="16">
         <v>2000</v>
       </c>
-      <c r="C17">
-        <v>1581.3399999999992</v>
+      <c r="C17" s="26">
+        <v>1432.5399999999993</v>
       </c>
       <c r="D17" s="18">
-        <v>0.79066999999999965</v>
+        <v>0.71626999999999963</v>
       </c>
       <c r="E17" s="16">
         <v>13</v>
       </c>
       <c r="F17" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="18">
-        <v>1</v>
+        <v>1.0769230769230769</v>
       </c>
       <c r="H17" s="17">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="I17" s="17">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="J17" s="18">
-        <v>1.0403225806451613</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="K17" s="16">
         <v>1</v>
       </c>
       <c r="L17" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17" s="18">
-        <v>1</v>
-      </c>
-      <c r="N17" s="16">
-        <v>1500</v>
+        <v>3</v>
+      </c>
+      <c r="N17">
+        <v>800</v>
       </c>
       <c r="O17" s="16">
-        <v>1559</v>
+        <v>662</v>
       </c>
       <c r="P17" s="18">
-        <f t="shared" si="1"/>
-        <v>1.0393333333333334</v>
-      </c>
-      <c r="Q17" s="16">
-        <v>183</v>
+        <v>0.82750000000000001</v>
+      </c>
+      <c r="Q17">
+        <v>70</v>
       </c>
       <c r="R17" s="16">
-        <v>239</v>
+        <v>51</v>
       </c>
       <c r="S17" s="18">
-        <v>1.3060109289617485</v>
+        <v>0.72857142857142854</v>
       </c>
       <c r="T17" s="24">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="U17" s="24">
-        <v>7386900</v>
+        <v>3201000</v>
       </c>
       <c r="V17" s="19">
-        <f t="shared" si="0"/>
-        <v>1.4773799999999999</v>
+        <v>0.80025000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B18" s="16">
         <v>1100</v>
       </c>
-      <c r="C18">
-        <v>1185.3199999999995</v>
+      <c r="C18" s="26">
+        <v>986.12000000000012</v>
       </c>
       <c r="D18" s="18">
-        <v>1.0775636363636358</v>
+        <v>0.89647272727272742</v>
       </c>
       <c r="E18" s="16">
         <v>16</v>
       </c>
       <c r="F18" s="16">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G18" s="18">
-        <v>2</v>
+        <v>1.4375</v>
       </c>
       <c r="H18" s="17">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="I18" s="17">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="J18" s="18">
-        <v>1.1263157894736842</v>
+        <v>0.7</v>
       </c>
       <c r="K18" s="16">
         <v>4</v>
       </c>
       <c r="L18" s="16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M18" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="N18" s="16">
-        <v>1500</v>
+        <v>1.25</v>
+      </c>
+      <c r="N18">
+        <v>1200</v>
       </c>
       <c r="O18" s="16">
-        <v>1507</v>
+        <v>1283</v>
       </c>
       <c r="P18" s="18">
-        <f t="shared" si="1"/>
-        <v>1.0046666666666666</v>
-      </c>
-      <c r="Q18" s="16">
-        <v>146</v>
+        <v>1.0691666666666666</v>
+      </c>
+      <c r="Q18">
+        <v>70</v>
       </c>
       <c r="R18" s="16">
-        <v>202</v>
+        <v>91</v>
       </c>
       <c r="S18" s="18">
-        <v>1.3835616438356164</v>
+        <v>1.3</v>
       </c>
       <c r="T18" s="24">
-        <v>2500000</v>
+        <v>2000000</v>
       </c>
       <c r="U18" s="24">
-        <v>9073900</v>
+        <v>971000</v>
       </c>
       <c r="V18" s="19">
-        <f t="shared" si="0"/>
-        <v>3.6295600000000001</v>
+        <v>0.48549999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B19" s="16">
         <v>2600</v>
       </c>
-      <c r="C19">
-        <v>2501.3799999999983</v>
+      <c r="C19" s="26">
+        <v>2381.8399999999988</v>
       </c>
       <c r="D19" s="18">
-        <v>0.96206923076923012</v>
+        <v>0.91609230769230721</v>
       </c>
       <c r="E19" s="16">
         <v>62</v>
       </c>
       <c r="F19" s="16">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G19" s="18">
-        <v>0.967741935483871</v>
+        <v>0.87096774193548387</v>
       </c>
       <c r="H19" s="17">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="I19" s="17">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="J19" s="18">
-        <v>0.8125</v>
+        <v>1.1454545454545455</v>
       </c>
       <c r="K19" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L19" s="16">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M19" s="18">
-        <v>1.6363636363636365</v>
-      </c>
-      <c r="N19" s="16">
+        <v>1.4166666666666667</v>
+      </c>
+      <c r="N19">
         <v>1500</v>
       </c>
       <c r="O19" s="16">
-        <v>1442</v>
+        <v>1508</v>
       </c>
       <c r="P19" s="18">
-        <f t="shared" si="1"/>
-        <v>0.96133333333333337</v>
-      </c>
-      <c r="Q19" s="16">
-        <v>198</v>
+        <v>1.0053333333333334</v>
+      </c>
+      <c r="Q19">
+        <v>210</v>
       </c>
       <c r="R19" s="16">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="S19" s="18">
-        <v>0.99494949494949492</v>
+        <v>1.019047619047619</v>
       </c>
       <c r="T19" s="24">
-        <v>5500000</v>
+        <v>4000000</v>
       </c>
       <c r="U19" s="24">
-        <v>4046999.9999000002</v>
+        <v>3186900</v>
       </c>
       <c r="V19" s="19">
-        <f t="shared" si="0"/>
-        <v>0.73581818180000003</v>
+        <v>0.79672500000000002</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B20" s="16">
-        <v>2200</v>
-      </c>
-      <c r="C20">
-        <v>2413.5599999999995</v>
+        <v>1000</v>
+      </c>
+      <c r="C20" s="26">
+        <v>383.1</v>
       </c>
       <c r="D20" s="18">
-        <v>1.097072727272727</v>
+        <v>0.38</v>
       </c>
       <c r="E20" s="16">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F20" s="16">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="G20" s="18">
-        <v>1.3529411764705883</v>
+        <v>0.2</v>
       </c>
       <c r="H20" s="17">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="I20" s="17">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="J20" s="18">
-        <v>0.90277777777777779</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="K20" s="16">
+        <v>4</v>
+      </c>
+      <c r="L20" s="16">
         <v>1</v>
       </c>
-      <c r="L20" s="16">
+      <c r="M20" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="N20">
         <v>0</v>
       </c>
-      <c r="M20" s="18">
+      <c r="O20" s="16">
         <v>0</v>
       </c>
-      <c r="N20" s="16">
-        <v>1500</v>
-      </c>
-      <c r="O20" s="16">
-        <v>1454</v>
-      </c>
       <c r="P20" s="18">
-        <f t="shared" si="1"/>
-        <v>0.96933333333333338</v>
-      </c>
-      <c r="Q20" s="16">
-        <v>151</v>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>70</v>
       </c>
       <c r="R20" s="16">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="S20" s="18">
-        <v>1.2516556291390728</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="T20" s="24">
-        <v>7000000</v>
+        <v>0</v>
       </c>
       <c r="U20" s="24">
-        <v>2273000</v>
+        <v>0</v>
       </c>
       <c r="V20" s="19">
-        <f t="shared" si="0"/>
-        <v>0.32471428571428573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
@@ -2080,69 +2048,67 @@
         <v>29</v>
       </c>
       <c r="B21" s="16">
-        <v>2650</v>
-      </c>
-      <c r="C21">
-        <v>1815.21</v>
+        <v>2200</v>
+      </c>
+      <c r="C21" s="26">
+        <v>1809.7099999999998</v>
       </c>
       <c r="D21" s="18">
-        <v>0.6849849056603774</v>
+        <v>0.82259545454545446</v>
       </c>
       <c r="E21" s="16">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F21" s="16">
+        <v>42</v>
+      </c>
+      <c r="G21" s="18">
+        <v>1.2352941176470589</v>
+      </c>
+      <c r="H21" s="17">
+        <v>60</v>
+      </c>
+      <c r="I21" s="17">
         <v>38</v>
       </c>
-      <c r="G21" s="18">
-        <v>1.2666666666666666</v>
-      </c>
-      <c r="H21" s="17">
-        <v>236</v>
-      </c>
-      <c r="I21" s="17">
-        <v>234</v>
-      </c>
       <c r="J21" s="18">
-        <v>0.99152542372881358</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="K21" s="16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L21" s="16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="N21" s="16">
-        <v>1500</v>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1200</v>
       </c>
       <c r="O21" s="16">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P21" s="18">
-        <f t="shared" si="1"/>
-        <v>0.62666666666666671</v>
-      </c>
-      <c r="Q21" s="16">
-        <v>192</v>
+        <v>0.78083333333333338</v>
+      </c>
+      <c r="Q21">
+        <v>200</v>
       </c>
       <c r="R21" s="16">
-        <v>521</v>
+        <v>248</v>
       </c>
       <c r="S21" s="18">
-        <v>2.7135416666666665</v>
+        <v>1.24</v>
       </c>
       <c r="T21" s="24">
-        <v>6500000</v>
+        <v>5500000</v>
       </c>
       <c r="U21" s="24">
-        <v>6256800</v>
+        <v>3440000</v>
       </c>
       <c r="V21" s="19">
-        <f t="shared" si="0"/>
-        <v>0.96258461538461537</v>
+        <v>0.62545454545454549</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
@@ -2150,69 +2116,67 @@
         <v>30</v>
       </c>
       <c r="B22" s="16">
-        <v>1600</v>
-      </c>
-      <c r="C22">
-        <v>1208.95</v>
+        <v>2650</v>
+      </c>
+      <c r="C22" s="26">
+        <v>2019.8000000000002</v>
       </c>
       <c r="D22" s="18">
-        <v>0.75559375000000006</v>
+        <v>0.76218867924528311</v>
       </c>
       <c r="E22" s="16">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F22" s="16">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G22" s="18">
-        <v>1.1818181818181819</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="H22" s="17">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="I22" s="17">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="J22" s="18">
-        <v>0.79729729729729726</v>
+        <v>1.2833333333333334</v>
       </c>
       <c r="K22" s="16">
         <v>6</v>
       </c>
       <c r="L22" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M22" s="18">
-        <v>1</v>
-      </c>
-      <c r="N22" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N22">
         <v>1500</v>
       </c>
       <c r="O22" s="16">
-        <v>1514</v>
+        <v>1611</v>
       </c>
       <c r="P22" s="18">
-        <f t="shared" si="1"/>
-        <v>1.0093333333333334</v>
-      </c>
-      <c r="Q22" s="16">
-        <v>181</v>
+        <v>1.0740000000000001</v>
+      </c>
+      <c r="Q22">
+        <v>120</v>
       </c>
       <c r="R22" s="16">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="S22" s="18">
-        <v>1.3259668508287292</v>
+        <v>1.1833333333333333</v>
       </c>
       <c r="T22" s="24">
-        <v>3600000</v>
+        <v>5500000</v>
       </c>
       <c r="U22" s="24">
-        <v>2956000</v>
+        <v>5511900</v>
       </c>
       <c r="V22" s="19">
-        <f t="shared" si="0"/>
-        <v>0.82111111111111112</v>
+        <v>1.0021636363636364</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
@@ -2220,161 +2184,229 @@
         <v>31</v>
       </c>
       <c r="B23" s="16">
-        <v>2200</v>
-      </c>
-      <c r="C23">
-        <v>2060.4899999999993</v>
+        <v>1600</v>
+      </c>
+      <c r="C23" s="26">
+        <v>1640.5599999999995</v>
       </c>
       <c r="D23" s="18">
-        <v>0.93658636363636338</v>
+        <v>1.0253499999999998</v>
       </c>
       <c r="E23" s="16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" s="16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G23" s="18">
-        <v>0.91304347826086951</v>
+        <v>1.0909090909090908</v>
       </c>
       <c r="H23" s="17">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="I23" s="17">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="J23" s="18">
-        <v>0.67391304347826086</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K23" s="16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L23" s="16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" s="18">
-        <v>0</v>
-      </c>
-      <c r="N23" s="16">
-        <v>1500</v>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="N23">
+        <v>1200</v>
       </c>
       <c r="O23" s="16">
-        <v>1537</v>
+        <v>1238</v>
       </c>
       <c r="P23" s="18">
-        <f t="shared" si="1"/>
-        <v>1.0246666666666666</v>
-      </c>
-      <c r="Q23" s="16">
-        <v>126</v>
+        <v>1.0316666666666667</v>
+      </c>
+      <c r="Q23">
+        <v>160</v>
       </c>
       <c r="R23" s="16">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="S23" s="18">
-        <v>1.246031746031746</v>
+        <v>1.14375</v>
       </c>
       <c r="T23" s="24">
-        <v>6500000</v>
+        <v>2000000</v>
       </c>
       <c r="U23" s="24">
-        <v>6392700</v>
+        <v>2195000</v>
       </c>
       <c r="V23" s="19">
-        <f t="shared" si="0"/>
-        <v>0.98349230769230767</v>
+        <v>1.0974999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="20">
-        <f>SUM(B2:B23)</f>
-        <v>53800</v>
-      </c>
-      <c r="C24" s="21">
-        <f>SUM(C2:C23)</f>
-        <v>51734.599999999991</v>
+      <c r="B24" s="16">
+        <v>2200</v>
+      </c>
+      <c r="C24" s="26">
+        <v>1697.2000000000003</v>
       </c>
       <c r="D24" s="18">
-        <f t="shared" ref="D24" si="2">C24/B24</f>
-        <v>0.96160966542750914</v>
-      </c>
-      <c r="E24" s="20">
-        <f>SUM(E2:E23)</f>
-        <v>840</v>
-      </c>
-      <c r="F24" s="20">
-        <f>SUM(F2:F23)</f>
-        <v>969</v>
+        <v>0.77145454545454561</v>
+      </c>
+      <c r="E24" s="16">
+        <v>23</v>
+      </c>
+      <c r="F24" s="16">
+        <v>22</v>
       </c>
       <c r="G24" s="18">
-        <f>F24/E24</f>
-        <v>1.1535714285714285</v>
-      </c>
-      <c r="H24" s="21">
-        <f>SUM(H2:H23)</f>
-        <v>1868</v>
-      </c>
-      <c r="I24" s="21">
-        <f>SUM(I2:I23)</f>
-        <v>1634</v>
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="H24" s="17">
+        <v>70</v>
+      </c>
+      <c r="I24" s="17">
+        <v>58</v>
       </c>
       <c r="J24" s="18">
-        <f t="shared" ref="J24" si="3">I24/H24</f>
-        <v>0.87473233404710926</v>
-      </c>
-      <c r="K24" s="20">
-        <f>SUM(K2:K23)</f>
-        <v>131</v>
-      </c>
-      <c r="L24" s="20">
-        <f>SUM(L2:L23)</f>
-        <v>158</v>
+        <v>0.82857142857142863</v>
+      </c>
+      <c r="K24" s="16">
+        <v>1</v>
+      </c>
+      <c r="L24" s="16">
+        <v>1</v>
       </c>
       <c r="M24" s="18">
-        <f t="shared" ref="M24" si="4">L24/K24</f>
-        <v>1.2061068702290076</v>
-      </c>
-      <c r="N24" s="20">
-        <f>SUM(N2:N23)</f>
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1200</v>
+      </c>
+      <c r="O24" s="16">
+        <v>1191</v>
+      </c>
+      <c r="P24" s="18">
+        <v>0.99250000000000005</v>
+      </c>
+      <c r="Q24">
+        <v>90</v>
+      </c>
+      <c r="R24" s="16">
+        <v>79</v>
+      </c>
+      <c r="S24" s="18">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="T24" s="24">
+        <v>6000000</v>
+      </c>
+      <c r="U24" s="24">
+        <v>5972000</v>
+      </c>
+      <c r="V24" s="19">
+        <v>0.99533333333333329</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="20">
+        <f>SUM(B2:B24)</f>
+        <v>54400</v>
+      </c>
+      <c r="C25" s="21">
+        <f>SUM(C2:C24)</f>
+        <v>48016.270000000011</v>
+      </c>
+      <c r="D25" s="18">
+        <f t="shared" ref="D25" si="0">C25/B25</f>
+        <v>0.88265202205882376</v>
+      </c>
+      <c r="E25" s="20">
+        <f>SUM(E2:E24)</f>
+        <v>835</v>
+      </c>
+      <c r="F25" s="20">
+        <f>SUM(F2:F24)</f>
+        <v>957</v>
+      </c>
+      <c r="G25" s="18">
+        <f>F25/E25</f>
+        <v>1.1461077844311378</v>
+      </c>
+      <c r="H25" s="21">
+        <f>SUM(H2:H24)</f>
+        <v>1667</v>
+      </c>
+      <c r="I25" s="21">
+        <f>SUM(I2:I24)</f>
+        <v>1521</v>
+      </c>
+      <c r="J25" s="18">
+        <f t="shared" ref="J25" si="1">I25/H25</f>
+        <v>0.91241751649670066</v>
+      </c>
+      <c r="K25" s="20">
+        <f>SUM(K2:K24)</f>
+        <v>140</v>
+      </c>
+      <c r="L25" s="20">
+        <f>SUM(L2:L24)</f>
+        <v>147</v>
+      </c>
+      <c r="M25" s="18">
+        <f t="shared" ref="M25" si="2">L25/K25</f>
+        <v>1.05</v>
+      </c>
+      <c r="N25" s="20">
+        <f>SUM(N2:N24)</f>
         <v>27700</v>
       </c>
-      <c r="O24" s="20">
-        <f>SUM(O2:O23)</f>
-        <v>23964</v>
-      </c>
-      <c r="P24" s="18">
-        <f t="shared" si="1"/>
-        <v>0.86512635379061376</v>
-      </c>
-      <c r="Q24" s="20">
-        <f>SUM(Q2:Q23)</f>
-        <v>2738</v>
-      </c>
-      <c r="R24" s="20">
-        <f>SUM(R2:R23)</f>
-        <v>3535</v>
-      </c>
-      <c r="S24" s="18">
-        <f t="shared" ref="S24" si="5">R24/Q24</f>
-        <v>1.2910883856829802</v>
-      </c>
-      <c r="T24" s="22">
-        <f>SUM(T2:T23)</f>
-        <v>138600000</v>
-      </c>
-      <c r="U24" s="22">
-        <f>SUM(U2:U23)</f>
-        <v>102851789.9999</v>
-      </c>
-      <c r="V24" s="19">
-        <f t="shared" si="0"/>
-        <v>0.74207640692568544</v>
+      <c r="O25" s="20">
+        <f>SUM(O2:O24)</f>
+        <v>25797</v>
+      </c>
+      <c r="P25" s="18">
+        <v>0.93129963898916968</v>
+      </c>
+      <c r="Q25" s="20">
+        <f>SUM(Q2:Q24)</f>
+        <v>3127</v>
+      </c>
+      <c r="R25" s="20">
+        <f>SUM(R2:R24)</f>
+        <v>3316</v>
+      </c>
+      <c r="S25" s="18">
+        <f t="shared" ref="S25" si="3">R25/Q25</f>
+        <v>1.0604413175567637</v>
+      </c>
+      <c r="T25" s="22">
+        <f>SUM(T2:T24)</f>
+        <v>108000000</v>
+      </c>
+      <c r="U25" s="22">
+        <f>SUM(U2:U24)</f>
+        <v>100251856</v>
+      </c>
+      <c r="V25" s="19">
+        <f t="shared" ref="V25" si="4">U25/T25</f>
+        <v>0.92825792592592593</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V24">
+    <sortCondition ref="A2:A24"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/general.xlsx
+++ b/data/general.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/06 Junio/Dasboatdde mayo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A3ACE78-EBBC-4B43-957D-324BB2EB68F8}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7C871AD-EF1D-45BB-AC05-40E8540408C5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F008453E-1A06-40CE-9AA2-8079F823278A}"/>
   </bookViews>
@@ -263,7 +263,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -341,26 +341,13 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="153">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -378,126 +365,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -563,136 +430,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -713,41 +450,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -763,811 +470,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1618,266 +525,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2350,8 +997,12 @@
       <c r="N2" s="23">
         <v>1500</v>
       </c>
-      <c r="O2" s="19"/>
-      <c r="P2" s="21"/>
+      <c r="O2" s="19">
+        <v>1583</v>
+      </c>
+      <c r="P2" s="21">
+        <v>1.0553333333333332</v>
+      </c>
       <c r="Q2" s="23">
         <v>95</v>
       </c>
@@ -2415,15 +1066,19 @@
       <c r="N3" s="23">
         <v>1500</v>
       </c>
-      <c r="O3" s="19"/>
-      <c r="P3" s="21"/>
+      <c r="O3" s="19">
+        <v>1543</v>
+      </c>
+      <c r="P3" s="21">
+        <v>1.0286666666666666</v>
+      </c>
       <c r="Q3" s="23">
         <v>150</v>
       </c>
       <c r="R3" s="19">
         <v>150</v>
       </c>
-      <c r="S3" s="29">
+      <c r="S3" s="21">
         <v>1</v>
       </c>
       <c r="T3" s="24">
@@ -2480,8 +1135,12 @@
       <c r="N4" s="23">
         <v>1500</v>
       </c>
-      <c r="O4" s="19"/>
-      <c r="P4" s="21"/>
+      <c r="O4" s="19">
+        <v>1578</v>
+      </c>
+      <c r="P4" s="21">
+        <v>1.052</v>
+      </c>
       <c r="Q4" s="23">
         <v>220</v>
       </c>
@@ -2545,8 +1204,12 @@
       <c r="N5" s="23">
         <v>0</v>
       </c>
-      <c r="O5" s="19"/>
-      <c r="P5" s="21"/>
+      <c r="O5" s="19">
+        <v>0</v>
+      </c>
+      <c r="P5" s="21">
+        <v>0</v>
+      </c>
       <c r="Q5" s="23">
         <v>25</v>
       </c>
@@ -2610,8 +1273,12 @@
       <c r="N6" s="23">
         <v>800</v>
       </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="21"/>
+      <c r="O6" s="19">
+        <v>741</v>
+      </c>
+      <c r="P6" s="21">
+        <v>0.92625000000000002</v>
+      </c>
       <c r="Q6" s="23">
         <v>135</v>
       </c>
@@ -2675,8 +1342,12 @@
       <c r="N7" s="23">
         <v>1500</v>
       </c>
-      <c r="O7" s="19"/>
-      <c r="P7" s="21"/>
+      <c r="O7" s="19">
+        <v>1144</v>
+      </c>
+      <c r="P7" s="21">
+        <v>0.76266666666666671</v>
+      </c>
       <c r="Q7" s="23">
         <v>180</v>
       </c>
@@ -2740,8 +1411,12 @@
       <c r="N8" s="23">
         <v>1200</v>
       </c>
-      <c r="O8" s="19"/>
-      <c r="P8" s="21"/>
+      <c r="O8" s="19">
+        <v>1222</v>
+      </c>
+      <c r="P8" s="21">
+        <v>1.0183333333333333</v>
+      </c>
       <c r="Q8" s="23">
         <v>60</v>
       </c>
@@ -2805,8 +1480,12 @@
       <c r="N9" s="23">
         <v>1200</v>
       </c>
-      <c r="O9" s="19"/>
-      <c r="P9" s="21"/>
+      <c r="O9" s="19">
+        <v>1225</v>
+      </c>
+      <c r="P9" s="21">
+        <v>1.0208333333333333</v>
+      </c>
       <c r="Q9" s="23">
         <v>80</v>
       </c>
@@ -2870,8 +1549,12 @@
       <c r="N10" s="23">
         <v>1500</v>
       </c>
-      <c r="O10" s="19"/>
-      <c r="P10" s="21"/>
+      <c r="O10" s="19">
+        <v>1394</v>
+      </c>
+      <c r="P10" s="21">
+        <v>0.92933333333333334</v>
+      </c>
       <c r="Q10" s="23">
         <v>180</v>
       </c>
@@ -2935,8 +1618,12 @@
       <c r="N11" s="23">
         <v>1500</v>
       </c>
-      <c r="O11" s="19"/>
-      <c r="P11" s="21"/>
+      <c r="O11" s="19">
+        <v>1153</v>
+      </c>
+      <c r="P11" s="21">
+        <v>0.76866666666666672</v>
+      </c>
       <c r="Q11" s="23">
         <v>190</v>
       </c>
@@ -3000,8 +1687,12 @@
       <c r="N12" s="23">
         <v>1500</v>
       </c>
-      <c r="O12" s="19"/>
-      <c r="P12" s="21"/>
+      <c r="O12" s="19">
+        <v>938</v>
+      </c>
+      <c r="P12" s="21">
+        <v>0.6253333333333333</v>
+      </c>
       <c r="Q12" s="23">
         <v>80</v>
       </c>
@@ -3065,8 +1756,12 @@
       <c r="N13" s="23">
         <v>1200</v>
       </c>
-      <c r="O13" s="19"/>
-      <c r="P13" s="21"/>
+      <c r="O13" s="19">
+        <v>1212</v>
+      </c>
+      <c r="P13" s="21">
+        <v>1.01</v>
+      </c>
       <c r="Q13" s="23">
         <v>130</v>
       </c>
@@ -3130,8 +1825,12 @@
       <c r="N14" s="23">
         <v>1500</v>
       </c>
-      <c r="O14" s="19"/>
-      <c r="P14" s="21"/>
+      <c r="O14" s="19">
+        <v>1548</v>
+      </c>
+      <c r="P14" s="21">
+        <v>1.032</v>
+      </c>
       <c r="Q14" s="23">
         <v>180</v>
       </c>
@@ -3195,8 +1894,12 @@
       <c r="N15" s="23">
         <v>1500</v>
       </c>
-      <c r="O15" s="19"/>
-      <c r="P15" s="21"/>
+      <c r="O15" s="19">
+        <v>743</v>
+      </c>
+      <c r="P15" s="21">
+        <v>0.49533333333333335</v>
+      </c>
       <c r="Q15" s="23">
         <v>450</v>
       </c>
@@ -3260,8 +1963,12 @@
       <c r="N16" s="23">
         <v>1200</v>
       </c>
-      <c r="O16" s="19"/>
-      <c r="P16" s="21"/>
+      <c r="O16" s="19">
+        <v>1201</v>
+      </c>
+      <c r="P16" s="21">
+        <v>1.0008333333333332</v>
+      </c>
       <c r="Q16" s="23">
         <v>70</v>
       </c>
@@ -3325,8 +2032,12 @@
       <c r="N17" s="23">
         <v>800</v>
       </c>
-      <c r="O17" s="19"/>
-      <c r="P17" s="21"/>
+      <c r="O17" s="19">
+        <v>809</v>
+      </c>
+      <c r="P17" s="21">
+        <v>1.01125</v>
+      </c>
       <c r="Q17" s="23">
         <v>70</v>
       </c>
@@ -3390,8 +2101,12 @@
       <c r="N18" s="23">
         <v>1200</v>
       </c>
-      <c r="O18" s="19"/>
-      <c r="P18" s="21"/>
+      <c r="O18" s="19">
+        <v>1243</v>
+      </c>
+      <c r="P18" s="21">
+        <v>1.0358333333333334</v>
+      </c>
       <c r="Q18" s="23">
         <v>70</v>
       </c>
@@ -3455,8 +2170,12 @@
       <c r="N19" s="23">
         <v>1500</v>
       </c>
-      <c r="O19" s="19"/>
-      <c r="P19" s="21"/>
+      <c r="O19" s="19">
+        <v>703</v>
+      </c>
+      <c r="P19" s="21">
+        <v>0.46866666666666668</v>
+      </c>
       <c r="Q19" s="23">
         <v>210</v>
       </c>
@@ -3520,8 +2239,12 @@
       <c r="N20" s="23">
         <v>0</v>
       </c>
-      <c r="O20" s="19"/>
-      <c r="P20" s="21"/>
+      <c r="O20" s="19">
+        <v>0</v>
+      </c>
+      <c r="P20" s="21">
+        <v>0</v>
+      </c>
       <c r="Q20" s="23">
         <v>70</v>
       </c>
@@ -3585,8 +2308,12 @@
       <c r="N21" s="23">
         <v>1200</v>
       </c>
-      <c r="O21" s="19"/>
-      <c r="P21" s="21"/>
+      <c r="O21" s="19">
+        <v>982</v>
+      </c>
+      <c r="P21" s="21">
+        <v>0.81833333333333336</v>
+      </c>
       <c r="Q21" s="23">
         <v>220</v>
       </c>
@@ -3650,8 +2377,12 @@
       <c r="N22" s="23">
         <v>1500</v>
       </c>
-      <c r="O22" s="19"/>
-      <c r="P22" s="21"/>
+      <c r="O22" s="19">
+        <v>1539</v>
+      </c>
+      <c r="P22" s="21">
+        <v>1.026</v>
+      </c>
       <c r="Q22" s="23">
         <v>140</v>
       </c>
@@ -3715,8 +2446,12 @@
       <c r="N23" s="23">
         <v>1200</v>
       </c>
-      <c r="O23" s="19"/>
-      <c r="P23" s="21"/>
+      <c r="O23" s="19">
+        <v>1196</v>
+      </c>
+      <c r="P23" s="21">
+        <v>0.9966666666666667</v>
+      </c>
       <c r="Q23" s="23">
         <v>160</v>
       </c>
@@ -3780,8 +2515,12 @@
       <c r="N24" s="23">
         <v>1200</v>
       </c>
-      <c r="O24" s="19"/>
-      <c r="P24" s="21"/>
+      <c r="O24" s="19">
+        <v>1371</v>
+      </c>
+      <c r="P24" s="21">
+        <v>1.1425000000000001</v>
+      </c>
       <c r="Q24" s="23">
         <v>90</v>
       </c>
@@ -3860,7 +2599,7 @@
       </c>
       <c r="O25" s="26">
         <f>SUM(O2:O24)</f>
-        <v>0</v>
+        <v>25068</v>
       </c>
       <c r="P25" s="21">
         <v>0.93129963898916968</v>
@@ -3894,80 +2633,87 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V24">
     <sortCondition ref="A2:A24"/>
   </sortState>
-  <conditionalFormatting sqref="D2:D25 G2:G25">
-    <cfRule type="cellIs" dxfId="32" priority="17" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25 M2:M25 S2:S25 P2:P25">
-    <cfRule type="cellIs" dxfId="31" priority="16" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V25">
-    <cfRule type="cellIs" dxfId="30" priority="15" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="12" operator="between">
-      <formula>0.9</formula>
-      <formula>0.99</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="11" operator="greaterThan">
-      <formula>0.99</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D2:D25 G2:G25 J2:J25 M2:M25 S2:S25">
-    <cfRule type="cellIs" dxfId="27" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="between">
       <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
-    <cfRule type="cellIs" dxfId="26" priority="13" operator="greaterThan">
+  <conditionalFormatting sqref="D2:D25 G2:G25">
+    <cfRule type="cellIs" dxfId="16" priority="19" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G25">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25 G2:G25 J2:J25 M2:M25 P2:P25 S2:S25 V2:V25">
-    <cfRule type="cellIs" dxfId="25" priority="10" operator="between">
+  <conditionalFormatting sqref="J2:J25 M2:M25 P2:P25">
+    <cfRule type="cellIs" dxfId="14" priority="18" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M25">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="greaterThan">
+      <formula>0.99</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S25 D2:D25 G2:G25 J2:J25 M2:M25 V2:V25 P2:P25">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="between">
       <formula>0.8</formula>
       <formula>0.88</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
-    <cfRule type="cellIs" dxfId="24" priority="9" operator="greaterThan">
+  <conditionalFormatting sqref="S2:S25">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="between">
+      <formula>0.79</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="between">
+      <formula>"79.9%"</formula>
+      <formula>"89.9%"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.89</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="between">
+      <formula>0.9</formula>
+      <formula>0.99</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="greaterThan">
+      <formula>0.99</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S22">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="lessThan">
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S25">
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="greaterThan">
+  <conditionalFormatting sqref="V2:V25">
+    <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="14" operator="between">
       <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
-      <formula>0.8</formula>
-      <formula>0.89</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
-      <formula>"79.9%"</formula>
-      <formula>"89.9%"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="between">
-      <formula>0.79</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="2" priority="17" operator="greaterThan">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S22">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="P2:P24">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="5" operator="between">
-      <formula>0.9</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P24">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/general.xlsx
+++ b/data/general.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/06 Junio/Dasboatdde mayo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/07 Julio/Dasboatdde junio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7C871AD-EF1D-45BB-AC05-40E8540408C5}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A46F1B3-48BF-4027-BAE1-803F1E397436}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F008453E-1A06-40CE-9AA2-8079F823278A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>CVS</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>San Cristobal</t>
+  </si>
+  <si>
+    <t>% puntos</t>
   </si>
 </sst>
 </file>
@@ -400,26 +403,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -475,6 +458,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -864,25 +867,26 @@
   <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" customWidth="1"/>
     <col min="10" max="10" width="9.140625" customWidth="1"/>
     <col min="11" max="11" width="8.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" customWidth="1"/>
     <col min="13" max="13" width="8.28515625" customWidth="1"/>
-    <col min="14" max="16" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="8.5703125" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" customWidth="1"/>
     <col min="19" max="19" width="7.7109375" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="2" customWidth="1"/>
+    <col min="20" max="21" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -897,7 +901,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>4</v>
@@ -962,65 +966,64 @@
         <v>2400</v>
       </c>
       <c r="C2" s="20">
-        <v>2559.1899999999991</v>
+        <v>2781.8900000000008</v>
       </c>
       <c r="D2" s="21">
-        <v>1.0663291666666663</v>
+        <v>1.1591208333333336</v>
       </c>
       <c r="E2" s="19">
         <v>30</v>
       </c>
       <c r="F2" s="19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" s="21">
-        <v>1.1333333333333333</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H2" s="22">
         <v>72</v>
       </c>
       <c r="I2" s="22">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="J2" s="21">
-        <v>1.0138888888888888</v>
+        <v>1.2083333333333333</v>
       </c>
       <c r="K2" s="19">
         <v>10</v>
       </c>
       <c r="L2" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2" s="21">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N2" s="23">
         <v>1500</v>
       </c>
       <c r="O2" s="19">
-        <v>1583</v>
+        <v>1616</v>
       </c>
       <c r="P2" s="21">
-        <v>1.0553333333333332</v>
+        <v>1.0773333333333333</v>
       </c>
       <c r="Q2" s="23">
         <v>95</v>
       </c>
       <c r="R2" s="19">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="S2" s="21">
-        <v>1.263157894736842</v>
+        <v>1.5263157894736843</v>
       </c>
       <c r="T2" s="24">
-        <v>8500000</v>
+        <v>9515700</v>
       </c>
       <c r="U2" s="24">
-        <v>9298202</v>
+        <v>9000000</v>
       </c>
       <c r="V2" s="25">
-        <f>U2/T2</f>
-        <v>1.0939061176470588</v>
+        <v>1.0572999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1031,46 +1034,46 @@
         <v>2850</v>
       </c>
       <c r="C3" s="20">
-        <v>2631.4900000000007</v>
+        <v>2489.9300000000003</v>
       </c>
       <c r="D3" s="21">
-        <v>0.92332982456140378</v>
+        <v>0.87365964912280714</v>
       </c>
       <c r="E3" s="19">
         <v>55</v>
       </c>
       <c r="F3" s="19">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G3" s="21">
-        <v>1</v>
+        <v>1.1090909090909091</v>
       </c>
       <c r="H3" s="22">
         <v>80</v>
       </c>
       <c r="I3" s="22">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="J3" s="21">
-        <v>1.325</v>
+        <v>0.85</v>
       </c>
       <c r="K3" s="19">
         <v>14</v>
       </c>
       <c r="L3" s="19">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M3" s="21">
-        <v>0.7857142857142857</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="N3" s="23">
-        <v>1500</v>
+        <v>848</v>
       </c>
       <c r="O3" s="19">
-        <v>1543</v>
+        <v>961</v>
       </c>
       <c r="P3" s="21">
-        <v>1.0286666666666666</v>
+        <v>1.133254716981132</v>
       </c>
       <c r="Q3" s="23">
         <v>150</v>
@@ -1082,14 +1085,13 @@
         <v>1</v>
       </c>
       <c r="T3" s="24">
+        <v>3183000</v>
+      </c>
+      <c r="U3" s="24">
         <v>4500000</v>
       </c>
-      <c r="U3" s="24">
-        <v>3392000</v>
-      </c>
       <c r="V3" s="25">
-        <f t="shared" ref="V3:V24" si="0">U3/T3</f>
-        <v>0.75377777777777777</v>
+        <v>0.70733333333333337</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -1100,65 +1102,64 @@
         <v>3700</v>
       </c>
       <c r="C4" s="20">
-        <v>2988.9500000000039</v>
+        <v>3472.6200000000035</v>
       </c>
       <c r="D4" s="21">
-        <v>0.80782432432432538</v>
+        <v>0.93854594594594687</v>
       </c>
       <c r="E4" s="19">
         <v>70</v>
       </c>
       <c r="F4" s="19">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G4" s="21">
-        <v>0.55714285714285716</v>
+        <v>0.81428571428571428</v>
       </c>
       <c r="H4" s="22">
         <v>125</v>
       </c>
       <c r="I4" s="22">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J4" s="21">
-        <v>1.008</v>
+        <v>0.96</v>
       </c>
       <c r="K4" s="19">
         <v>10</v>
       </c>
       <c r="L4" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M4" s="21">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="N4" s="23">
         <v>1500</v>
       </c>
       <c r="O4" s="19">
-        <v>1578</v>
+        <v>1523</v>
       </c>
       <c r="P4" s="21">
-        <v>1.052</v>
+        <v>1.0153333333333334</v>
       </c>
       <c r="Q4" s="23">
         <v>220</v>
       </c>
       <c r="R4" s="19">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="S4" s="21">
-        <v>0.90454545454545454</v>
+        <v>1.1136363636363635</v>
       </c>
       <c r="T4" s="24">
+        <v>8470815.2300000004</v>
+      </c>
+      <c r="U4" s="24">
         <v>9500000</v>
       </c>
-      <c r="U4" s="24">
-        <v>7926000</v>
-      </c>
       <c r="V4" s="25">
-        <f t="shared" si="0"/>
-        <v>0.83431578947368423</v>
+        <v>0.89166476105263159</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1169,10 +1170,10 @@
         <v>1000</v>
       </c>
       <c r="C5" s="20">
-        <v>1069.5199999999998</v>
+        <v>611.49000000000012</v>
       </c>
       <c r="D5" s="21">
-        <v>1.0695199999999998</v>
+        <v>0.61149000000000009</v>
       </c>
       <c r="E5" s="19">
         <v>8</v>
@@ -1187,19 +1188,19 @@
         <v>40</v>
       </c>
       <c r="I5" s="22">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J5" s="21">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="K5" s="19">
         <v>2</v>
       </c>
       <c r="L5" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N5" s="23">
         <v>0</v>
@@ -1214,20 +1215,19 @@
         <v>25</v>
       </c>
       <c r="R5" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S5" s="21">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="T5" s="24">
+        <v>1386900</v>
+      </c>
+      <c r="U5" s="24">
         <v>2500000</v>
       </c>
-      <c r="U5" s="24">
-        <v>1741000</v>
-      </c>
       <c r="V5" s="25">
-        <f t="shared" si="0"/>
-        <v>0.69640000000000002</v>
+        <v>0.55476000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1238,65 +1238,64 @@
         <v>1500</v>
       </c>
       <c r="C6" s="20">
-        <v>1644.8199999999995</v>
+        <v>1145.6399999999999</v>
       </c>
       <c r="D6" s="21">
-        <v>1.0965466666666663</v>
+        <v>0.76375999999999988</v>
       </c>
       <c r="E6" s="19">
         <v>25</v>
       </c>
       <c r="F6" s="19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="21">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="22">
         <v>50</v>
       </c>
       <c r="I6" s="22">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="J6" s="21">
-        <v>1.38</v>
+        <v>0.78</v>
       </c>
       <c r="K6" s="19">
         <v>1</v>
       </c>
       <c r="L6" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="23">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="O6" s="19">
-        <v>741</v>
+        <v>1058</v>
       </c>
       <c r="P6" s="21">
-        <v>0.92625000000000002</v>
+        <v>0.88166666666666671</v>
       </c>
       <c r="Q6" s="23">
         <v>135</v>
       </c>
       <c r="R6" s="19">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="S6" s="21">
-        <v>0.97777777777777775</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="T6" s="24">
-        <v>5000000</v>
+        <v>4421900</v>
       </c>
       <c r="U6" s="24">
-        <v>5336500</v>
+        <v>5500000</v>
       </c>
       <c r="V6" s="25">
-        <f t="shared" si="0"/>
-        <v>1.0672999999999999</v>
+        <v>0.80398181818181813</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1307,28 +1306,28 @@
         <v>3000</v>
       </c>
       <c r="C7" s="20">
-        <v>3374.9700000000007</v>
+        <v>3341.1700000000005</v>
       </c>
       <c r="D7" s="21">
-        <v>1.1249900000000002</v>
+        <v>1.1137233333333334</v>
       </c>
       <c r="E7" s="19">
         <v>55</v>
       </c>
       <c r="F7" s="19">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G7" s="21">
-        <v>1.1818181818181819</v>
+        <v>0.98181818181818181</v>
       </c>
       <c r="H7" s="22">
         <v>95</v>
       </c>
       <c r="I7" s="22">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J7" s="21">
-        <v>0.97894736842105268</v>
+        <v>1.0210526315789474</v>
       </c>
       <c r="K7" s="19">
         <v>14</v>
@@ -1340,32 +1339,31 @@
         <v>1.4285714285714286</v>
       </c>
       <c r="N7" s="23">
-        <v>1500</v>
+        <v>848</v>
       </c>
       <c r="O7" s="19">
-        <v>1144</v>
+        <v>1273</v>
       </c>
       <c r="P7" s="21">
-        <v>0.76266666666666671</v>
+        <v>1.5011792452830188</v>
       </c>
       <c r="Q7" s="23">
         <v>180</v>
       </c>
       <c r="R7" s="19">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="S7" s="21">
-        <v>0.89444444444444449</v>
+        <v>1</v>
       </c>
       <c r="T7" s="24">
-        <v>9000000</v>
+        <v>10228200.079999998</v>
       </c>
       <c r="U7" s="24">
-        <v>7002400</v>
+        <v>8000000</v>
       </c>
       <c r="V7" s="25">
-        <f t="shared" si="0"/>
-        <v>0.77804444444444443</v>
+        <v>1.2785250099999999</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1376,28 +1374,28 @@
         <v>1450</v>
       </c>
       <c r="C8" s="20">
-        <v>1128.4999999999998</v>
+        <v>940.4799999999999</v>
       </c>
       <c r="D8" s="21">
-        <v>0.77827586206896537</v>
+        <v>0.6486068965517241</v>
       </c>
       <c r="E8" s="19">
         <v>15</v>
       </c>
       <c r="F8" s="19">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8" s="21">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H8" s="22">
         <v>50</v>
       </c>
       <c r="I8" s="22">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J8" s="21">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="K8" s="19">
         <v>1</v>
@@ -1409,32 +1407,31 @@
         <v>0</v>
       </c>
       <c r="N8" s="23">
-        <v>1200</v>
+        <v>417</v>
       </c>
       <c r="O8" s="19">
-        <v>1222</v>
+        <v>371</v>
       </c>
       <c r="P8" s="21">
-        <v>1.0183333333333333</v>
+        <v>0.88968824940047964</v>
       </c>
       <c r="Q8" s="23">
         <v>60</v>
       </c>
       <c r="R8" s="19">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S8" s="21">
-        <v>1.3333333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="T8" s="24">
-        <v>2500000</v>
+        <v>1398000</v>
       </c>
       <c r="U8" s="24">
-        <v>2970000</v>
+        <v>3000000</v>
       </c>
       <c r="V8" s="25">
-        <f t="shared" si="0"/>
-        <v>1.1879999999999999</v>
+        <v>0.46600000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -1445,65 +1442,64 @@
         <v>1500</v>
       </c>
       <c r="C9" s="20">
-        <v>1847.329999999999</v>
+        <v>1084.3</v>
       </c>
       <c r="D9" s="21">
-        <v>1.2315533333333326</v>
+        <v>0.72286666666666666</v>
       </c>
       <c r="E9" s="19">
         <v>37</v>
       </c>
       <c r="F9" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G9" s="21">
-        <v>1.1891891891891893</v>
+        <v>0.89189189189189189</v>
       </c>
       <c r="H9" s="22">
         <v>45</v>
       </c>
       <c r="I9" s="22">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J9" s="21">
-        <v>1.0666666666666667</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="K9" s="19">
         <v>1</v>
       </c>
       <c r="L9" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" s="23">
         <v>1200</v>
       </c>
       <c r="O9" s="19">
-        <v>1225</v>
+        <v>804</v>
       </c>
       <c r="P9" s="21">
-        <v>1.0208333333333333</v>
+        <v>0.67</v>
       </c>
       <c r="Q9" s="23">
         <v>80</v>
       </c>
       <c r="R9" s="19">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="S9" s="21">
-        <v>1.425</v>
+        <v>1.0874999999999999</v>
       </c>
       <c r="T9" s="24">
-        <v>5000000</v>
+        <v>3948900</v>
       </c>
       <c r="U9" s="24">
-        <v>5292000</v>
+        <v>5500000</v>
       </c>
       <c r="V9" s="25">
-        <f t="shared" si="0"/>
-        <v>1.0584</v>
+        <v>0.71798181818181817</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1514,28 +1510,28 @@
         <v>4000</v>
       </c>
       <c r="C10" s="20">
-        <v>3237.2900000000027</v>
+        <v>3196.6400000000035</v>
       </c>
       <c r="D10" s="21">
-        <v>0.80932250000000072</v>
+        <v>0.79916000000000087</v>
       </c>
       <c r="E10" s="19">
         <v>50</v>
       </c>
       <c r="F10" s="19">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G10" s="21">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="H10" s="22">
         <v>130</v>
       </c>
       <c r="I10" s="22">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="J10" s="21">
-        <v>1.0538461538461539</v>
+        <v>0.86923076923076925</v>
       </c>
       <c r="K10" s="19">
         <v>1</v>
@@ -1550,29 +1546,28 @@
         <v>1500</v>
       </c>
       <c r="O10" s="19">
-        <v>1394</v>
+        <v>1263</v>
       </c>
       <c r="P10" s="21">
-        <v>0.92933333333333334</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="Q10" s="23">
         <v>180</v>
       </c>
       <c r="R10" s="19">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="S10" s="21">
-        <v>1.1888888888888889</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="T10" s="24">
-        <v>7000000</v>
+        <v>5826700</v>
       </c>
       <c r="U10" s="24">
-        <v>8537000</v>
+        <v>7500000</v>
       </c>
       <c r="V10" s="25">
-        <f t="shared" si="0"/>
-        <v>1.2195714285714285</v>
+        <v>0.77689333333333332</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1583,65 +1578,64 @@
         <v>3500</v>
       </c>
       <c r="C11" s="20">
-        <v>3217.0300000000029</v>
+        <v>3222.8200000000033</v>
       </c>
       <c r="D11" s="21">
-        <v>0.9191514285714294</v>
+        <v>0.92080571428571523</v>
       </c>
       <c r="E11" s="19">
         <v>80</v>
       </c>
       <c r="F11" s="19">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G11" s="21">
-        <v>1.075</v>
+        <v>0.95</v>
       </c>
       <c r="H11" s="22">
         <v>90</v>
       </c>
       <c r="I11" s="22">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J11" s="21">
-        <v>0.91111111111111109</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="K11" s="19">
         <v>20</v>
       </c>
       <c r="L11" s="19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M11" s="21">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="N11" s="23">
         <v>1500</v>
       </c>
       <c r="O11" s="19">
-        <v>1153</v>
+        <v>1515</v>
       </c>
       <c r="P11" s="21">
-        <v>0.76866666666666672</v>
+        <v>1.01</v>
       </c>
       <c r="Q11" s="23">
         <v>190</v>
       </c>
       <c r="R11" s="19">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="S11" s="21">
-        <v>1.1842105263157894</v>
+        <v>1.168421052631579</v>
       </c>
       <c r="T11" s="24">
-        <v>4000000</v>
+        <v>3107000</v>
       </c>
       <c r="U11" s="24">
-        <v>3728800</v>
+        <v>4500000</v>
       </c>
       <c r="V11" s="25">
-        <f t="shared" si="0"/>
-        <v>0.93220000000000003</v>
+        <v>0.69044444444444442</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1652,28 +1646,28 @@
         <v>2400</v>
       </c>
       <c r="C12" s="20">
-        <v>2701.0300000000025</v>
+        <v>2358.04</v>
       </c>
       <c r="D12" s="21">
-        <v>1.1254291666666676</v>
+        <v>0.9825166666666667</v>
       </c>
       <c r="E12" s="19">
         <v>24</v>
       </c>
       <c r="F12" s="19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G12" s="21">
-        <v>0.95833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H12" s="22">
         <v>110</v>
       </c>
       <c r="I12" s="22">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="J12" s="21">
-        <v>1.2818181818181817</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="K12" s="19">
         <v>1</v>
@@ -1688,29 +1682,28 @@
         <v>1500</v>
       </c>
       <c r="O12" s="19">
-        <v>938</v>
+        <v>756</v>
       </c>
       <c r="P12" s="21">
-        <v>0.6253333333333333</v>
+        <v>0.504</v>
       </c>
       <c r="Q12" s="23">
         <v>80</v>
       </c>
       <c r="R12" s="19">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="S12" s="21">
-        <v>1.0625</v>
+        <v>0.96250000000000002</v>
       </c>
       <c r="T12" s="24">
-        <v>8000000</v>
+        <v>8615004.3800000008</v>
       </c>
       <c r="U12" s="24">
-        <v>8106000</v>
+        <v>8500000</v>
       </c>
       <c r="V12" s="25">
-        <f t="shared" si="0"/>
-        <v>1.01325</v>
+        <v>1.0135299270588236</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1721,65 +1714,64 @@
         <v>2000</v>
       </c>
       <c r="C13" s="20">
-        <v>2085.2499999999991</v>
+        <v>1384.7</v>
       </c>
       <c r="D13" s="21">
-        <v>1.0426249999999995</v>
+        <v>0.69235000000000002</v>
       </c>
       <c r="E13" s="19">
         <v>35</v>
       </c>
       <c r="F13" s="19">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G13" s="21">
-        <v>1.0571428571428572</v>
+        <v>0.82857142857142863</v>
       </c>
       <c r="H13" s="22">
         <v>50</v>
       </c>
       <c r="I13" s="22">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J13" s="21">
-        <v>1.2</v>
+        <v>0.88</v>
       </c>
       <c r="K13" s="19">
         <v>8</v>
       </c>
       <c r="L13" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M13" s="21">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="N13" s="23">
         <v>1200</v>
       </c>
       <c r="O13" s="19">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="P13" s="21">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="Q13" s="23">
         <v>130</v>
       </c>
       <c r="R13" s="19">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S13" s="21">
-        <v>1.0461538461538462</v>
+        <v>1.0384615384615385</v>
       </c>
       <c r="T13" s="24">
-        <v>5000000</v>
+        <v>5368500</v>
       </c>
       <c r="U13" s="24">
-        <v>5512700</v>
+        <v>5500000</v>
       </c>
       <c r="V13" s="25">
-        <f t="shared" si="0"/>
-        <v>1.1025400000000001</v>
+        <v>0.97609090909090912</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1790,19 +1782,19 @@
         <v>2500</v>
       </c>
       <c r="C14" s="20">
-        <v>2332.6699999999996</v>
+        <v>2691.0300000000016</v>
       </c>
       <c r="D14" s="21">
-        <v>0.9330679999999999</v>
+        <v>1.0764120000000006</v>
       </c>
       <c r="E14" s="19">
         <v>50</v>
       </c>
       <c r="F14" s="19">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G14" s="21">
-        <v>0.98</v>
+        <v>1.54</v>
       </c>
       <c r="H14" s="22">
         <v>75</v>
@@ -1817,38 +1809,37 @@
         <v>12</v>
       </c>
       <c r="L14" s="19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M14" s="21">
-        <v>0.5</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="N14" s="23">
         <v>1500</v>
       </c>
       <c r="O14" s="19">
-        <v>1548</v>
+        <v>1491</v>
       </c>
       <c r="P14" s="21">
-        <v>1.032</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="Q14" s="23">
         <v>180</v>
       </c>
       <c r="R14" s="19">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="S14" s="21">
-        <v>0.97222222222222221</v>
+        <v>1.0277777777777777</v>
       </c>
       <c r="T14" s="24">
-        <v>3500000</v>
+        <v>1570000</v>
       </c>
       <c r="U14" s="24">
-        <v>1525000</v>
+        <v>3000000</v>
       </c>
       <c r="V14" s="25">
-        <f t="shared" si="0"/>
-        <v>0.43571428571428572</v>
+        <v>0.52333333333333332</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1859,65 +1850,64 @@
         <v>6800</v>
       </c>
       <c r="C15" s="20">
-        <v>7198.1400000000076</v>
+        <v>7204.5600000000031</v>
       </c>
       <c r="D15" s="21">
-        <v>1.0585500000000012</v>
+        <v>1.0594941176470594</v>
       </c>
       <c r="E15" s="19">
         <v>140</v>
       </c>
       <c r="F15" s="19">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G15" s="21">
-        <v>1.2</v>
+        <v>1.1571428571428573</v>
       </c>
       <c r="H15" s="22">
         <v>220</v>
       </c>
       <c r="I15" s="22">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="J15" s="21">
-        <v>1.1409090909090909</v>
+        <v>1.0681818181818181</v>
       </c>
       <c r="K15" s="19">
         <v>14</v>
       </c>
       <c r="L15" s="19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M15" s="21">
-        <v>0.6428571428571429</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="N15" s="23">
         <v>1500</v>
       </c>
       <c r="O15" s="19">
-        <v>743</v>
+        <v>1786</v>
       </c>
       <c r="P15" s="21">
-        <v>0.49533333333333335</v>
+        <v>1.1906666666666668</v>
       </c>
       <c r="Q15" s="23">
         <v>450</v>
       </c>
       <c r="R15" s="19">
-        <v>498</v>
+        <v>452</v>
       </c>
       <c r="S15" s="21">
-        <v>1.1066666666666667</v>
+        <v>1.0044444444444445</v>
       </c>
       <c r="T15" s="24">
-        <v>6500000</v>
+        <v>8189563.1500000004</v>
       </c>
       <c r="U15" s="24">
-        <v>6644800</v>
+        <v>7000000</v>
       </c>
       <c r="V15" s="25">
-        <f t="shared" si="0"/>
-        <v>1.0222769230769231</v>
+        <v>1.1699375928571429</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1928,28 +1918,28 @@
         <v>1500</v>
       </c>
       <c r="C16" s="20">
-        <v>757.01</v>
+        <v>928.37999999999988</v>
       </c>
       <c r="D16" s="21">
-        <v>0.50467333333333331</v>
+        <v>0.61891999999999991</v>
       </c>
       <c r="E16" s="19">
         <v>15</v>
       </c>
       <c r="F16" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="21">
-        <v>1.1333333333333333</v>
+        <v>1.2</v>
       </c>
       <c r="H16" s="22">
         <v>30</v>
       </c>
       <c r="I16" s="22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16" s="21">
-        <v>0.83333333333333337</v>
+        <v>0.8</v>
       </c>
       <c r="K16" s="19">
         <v>8</v>
@@ -1964,29 +1954,28 @@
         <v>1200</v>
       </c>
       <c r="O16" s="19">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="P16" s="21">
-        <v>1.0008333333333332</v>
+        <v>1.0016666666666667</v>
       </c>
       <c r="Q16" s="23">
         <v>70</v>
       </c>
       <c r="R16" s="19">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="S16" s="21">
-        <v>0.58571428571428574</v>
+        <v>1.0142857142857142</v>
       </c>
       <c r="T16" s="24">
+        <v>910897.93</v>
+      </c>
+      <c r="U16" s="24">
         <v>2500000</v>
       </c>
-      <c r="U16" s="24">
-        <v>1752002.15</v>
-      </c>
       <c r="V16" s="25">
-        <f t="shared" si="0"/>
-        <v>0.70080085999999997</v>
+        <v>0.36435917200000001</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -1997,65 +1986,64 @@
         <v>2000</v>
       </c>
       <c r="C17" s="20">
-        <v>1368.6599999999994</v>
+        <v>1478.3299999999992</v>
       </c>
       <c r="D17" s="21">
-        <v>0.68432999999999966</v>
+        <v>0.73916499999999963</v>
       </c>
       <c r="E17" s="19">
         <v>15</v>
       </c>
       <c r="F17" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G17" s="21">
-        <v>0.93333333333333335</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="H17" s="22">
         <v>75</v>
       </c>
       <c r="I17" s="22">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J17" s="21">
-        <v>0.73333333333333328</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="K17" s="19">
         <v>1</v>
       </c>
       <c r="L17" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M17" s="21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N17" s="23">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="O17" s="19">
-        <v>809</v>
+        <v>1097</v>
       </c>
       <c r="P17" s="21">
-        <v>1.01125</v>
+        <v>0.91416666666666668</v>
       </c>
       <c r="Q17" s="23">
         <v>70</v>
       </c>
       <c r="R17" s="19">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="S17" s="21">
-        <v>1.0428571428571429</v>
+        <v>1.3571428571428572</v>
       </c>
       <c r="T17" s="24">
-        <v>4000000</v>
+        <v>3376702.15</v>
       </c>
       <c r="U17" s="24">
-        <v>3829900</v>
+        <v>4500000</v>
       </c>
       <c r="V17" s="25">
-        <f t="shared" si="0"/>
-        <v>0.95747499999999997</v>
+        <v>0.75037825555555548</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -2066,65 +2054,64 @@
         <v>1100</v>
       </c>
       <c r="C18" s="20">
-        <v>996.1600000000002</v>
+        <v>1050.2500000000002</v>
       </c>
       <c r="D18" s="21">
-        <v>0.90560000000000018</v>
+        <v>0.95477272727272744</v>
       </c>
       <c r="E18" s="19">
         <v>20</v>
       </c>
       <c r="F18" s="19">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G18" s="21">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="22">
         <v>30</v>
       </c>
       <c r="I18" s="22">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J18" s="21">
-        <v>0.9</v>
+        <v>1.2333333333333334</v>
       </c>
       <c r="K18" s="19">
         <v>4</v>
       </c>
       <c r="L18" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" s="21">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N18" s="23">
-        <v>1200</v>
+        <v>835</v>
       </c>
       <c r="O18" s="19">
-        <v>1243</v>
+        <v>594</v>
       </c>
       <c r="P18" s="21">
-        <v>1.0358333333333334</v>
+        <v>0.71137724550898207</v>
       </c>
       <c r="Q18" s="23">
         <v>70</v>
       </c>
       <c r="R18" s="19">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="S18" s="21">
-        <v>1.1714285714285715</v>
+        <v>1.2285714285714286</v>
       </c>
       <c r="T18" s="24">
+        <v>1483002.15</v>
+      </c>
+      <c r="U18" s="24">
         <v>2000000</v>
       </c>
-      <c r="U18" s="24">
-        <v>777000</v>
-      </c>
       <c r="V18" s="25">
-        <f t="shared" si="0"/>
-        <v>0.38850000000000001</v>
+        <v>0.74150107499999995</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -2135,65 +2122,64 @@
         <v>2600</v>
       </c>
       <c r="C19" s="20">
-        <v>1879.7399999999991</v>
+        <v>2194.4999999999986</v>
       </c>
       <c r="D19" s="21">
-        <v>0.72297692307692274</v>
+        <v>0.84403846153846096</v>
       </c>
       <c r="E19" s="19">
         <v>62</v>
       </c>
       <c r="F19" s="19">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G19" s="21">
-        <v>0.77419354838709675</v>
+        <v>0.88709677419354838</v>
       </c>
       <c r="H19" s="22">
         <v>60</v>
       </c>
       <c r="I19" s="22">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J19" s="21">
-        <v>0.71666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="K19" s="19">
         <v>14</v>
       </c>
       <c r="L19" s="19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="21">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
       <c r="N19" s="23">
-        <v>1500</v>
+        <v>913</v>
       </c>
       <c r="O19" s="19">
-        <v>703</v>
+        <v>487</v>
       </c>
       <c r="P19" s="21">
-        <v>0.46866666666666668</v>
+        <v>0.53340635268346115</v>
       </c>
       <c r="Q19" s="23">
         <v>210</v>
       </c>
       <c r="R19" s="19">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="S19" s="21">
-        <v>0.79523809523809519</v>
+        <v>0.85238095238095235</v>
       </c>
       <c r="T19" s="24">
+        <v>1939902.15</v>
+      </c>
+      <c r="U19" s="24">
         <v>4000000</v>
       </c>
-      <c r="U19" s="24">
-        <v>1814000</v>
-      </c>
       <c r="V19" s="25">
-        <f t="shared" si="0"/>
-        <v>0.45350000000000001</v>
+        <v>0.4849755375</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -2204,37 +2190,37 @@
         <v>1000</v>
       </c>
       <c r="C20" s="20">
-        <v>875.25000000000011</v>
+        <v>761.31999999999982</v>
       </c>
       <c r="D20" s="21">
-        <v>0.87525000000000008</v>
+        <v>0.76131999999999977</v>
       </c>
       <c r="E20" s="19">
         <v>15</v>
       </c>
       <c r="F20" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G20" s="21">
-        <v>0.66666666666666663</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="H20" s="22">
         <v>30</v>
       </c>
       <c r="I20" s="22">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J20" s="21">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="K20" s="19">
         <v>4</v>
       </c>
       <c r="L20" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20" s="21">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="N20" s="23">
         <v>0</v>
@@ -2249,20 +2235,19 @@
         <v>70</v>
       </c>
       <c r="R20" s="19">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="S20" s="21">
-        <v>0.9285714285714286</v>
+        <v>0.82857142857142863</v>
       </c>
       <c r="T20" s="24">
-        <v>3000000</v>
+        <v>1684550</v>
       </c>
       <c r="U20" s="24">
-        <v>953000</v>
+        <v>2500000</v>
       </c>
       <c r="V20" s="25">
-        <f t="shared" si="0"/>
-        <v>0.31766666666666665</v>
+        <v>0.67381999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -2273,28 +2258,28 @@
         <v>2200</v>
       </c>
       <c r="C21" s="20">
-        <v>1930.3599999999997</v>
+        <v>2372.1799999999998</v>
       </c>
       <c r="D21" s="21">
-        <v>0.87743636363636346</v>
+        <v>1.0782636363636362</v>
       </c>
       <c r="E21" s="19">
         <v>40</v>
       </c>
       <c r="F21" s="19">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G21" s="21">
-        <v>1.4750000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="H21" s="22">
         <v>60</v>
       </c>
       <c r="I21" s="22">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="J21" s="21">
-        <v>0.68333333333333335</v>
+        <v>0.98333333333333328</v>
       </c>
       <c r="K21" s="19">
         <v>1</v>
@@ -2309,29 +2294,28 @@
         <v>1200</v>
       </c>
       <c r="O21" s="19">
-        <v>982</v>
+        <v>839</v>
       </c>
       <c r="P21" s="21">
-        <v>0.81833333333333336</v>
+        <v>0.69916666666666671</v>
       </c>
       <c r="Q21" s="23">
         <v>220</v>
       </c>
       <c r="R21" s="19">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="S21" s="21">
-        <v>1.0772727272727274</v>
+        <v>0.90454545454545454</v>
       </c>
       <c r="T21" s="24">
+        <v>4621656</v>
+      </c>
+      <c r="U21" s="24">
         <v>5500000</v>
       </c>
-      <c r="U21" s="24">
-        <v>5477900</v>
-      </c>
       <c r="V21" s="25">
-        <f t="shared" si="0"/>
-        <v>0.99598181818181819</v>
+        <v>0.84030109090909089</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
@@ -2342,65 +2326,64 @@
         <v>2650</v>
       </c>
       <c r="C22" s="20">
-        <v>1824.6599999999999</v>
+        <v>2035.7799999999995</v>
       </c>
       <c r="D22" s="21">
-        <v>0.68855094339622636</v>
+        <v>0.76821886792452809</v>
       </c>
       <c r="E22" s="19">
         <v>35</v>
       </c>
       <c r="F22" s="19">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G22" s="21">
-        <v>0.91428571428571426</v>
+        <v>1.3714285714285714</v>
       </c>
       <c r="H22" s="22">
         <v>70</v>
       </c>
       <c r="I22" s="22">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J22" s="21">
-        <v>1.0714285714285714</v>
+        <v>1.0285714285714285</v>
       </c>
       <c r="K22" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="21">
-        <v>0.16666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N22" s="23">
         <v>1500</v>
       </c>
       <c r="O22" s="19">
-        <v>1539</v>
+        <v>1434</v>
       </c>
       <c r="P22" s="21">
-        <v>1.026</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="Q22" s="23">
         <v>140</v>
       </c>
       <c r="R22" s="19">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="S22" s="21">
-        <v>0.99285714285714288</v>
+        <v>1.0142857142857142</v>
       </c>
       <c r="T22" s="24">
-        <v>6000000</v>
+        <v>4369512.93</v>
       </c>
       <c r="U22" s="24">
-        <v>4803000</v>
+        <v>5500000</v>
       </c>
       <c r="V22" s="25">
-        <f t="shared" si="0"/>
-        <v>0.80049999999999999</v>
+        <v>0.79445689636363626</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -2411,65 +2394,64 @@
         <v>1800</v>
       </c>
       <c r="C23" s="20">
-        <v>1577.5899999999997</v>
+        <v>1038.83</v>
       </c>
       <c r="D23" s="21">
-        <v>0.87643888888888877</v>
+        <v>0.57712777777777768</v>
       </c>
       <c r="E23" s="19">
         <v>30</v>
       </c>
       <c r="F23" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G23" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="H23" s="22">
         <v>55</v>
       </c>
       <c r="I23" s="22">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="J23" s="21">
-        <v>1.0363636363636364</v>
+        <v>0.61818181818181817</v>
       </c>
       <c r="K23" s="19">
         <v>8</v>
       </c>
       <c r="L23" s="19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M23" s="21">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="N23" s="23">
-        <v>1200</v>
+        <v>1043</v>
       </c>
       <c r="O23" s="19">
-        <v>1196</v>
+        <v>831</v>
       </c>
       <c r="P23" s="21">
-        <v>0.9966666666666667</v>
+        <v>0.79674017257909879</v>
       </c>
       <c r="Q23" s="23">
         <v>160</v>
       </c>
       <c r="R23" s="19">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="S23" s="21">
-        <v>1.05</v>
+        <v>1.15625</v>
       </c>
       <c r="T23" s="24">
+        <v>2139300</v>
+      </c>
+      <c r="U23" s="24">
         <v>4000000</v>
       </c>
-      <c r="U23" s="24">
-        <v>3487500</v>
-      </c>
       <c r="V23" s="25">
-        <f t="shared" si="0"/>
-        <v>0.87187499999999996</v>
+        <v>0.53482499999999999</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -2480,65 +2462,64 @@
         <v>2200</v>
       </c>
       <c r="C24" s="20">
-        <v>1854.7499999999995</v>
+        <v>1270.5899999999997</v>
       </c>
       <c r="D24" s="21">
-        <v>0.84306818181818166</v>
+        <v>0.57754090909090894</v>
       </c>
       <c r="E24" s="19">
         <v>24</v>
       </c>
       <c r="F24" s="19">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G24" s="21">
-        <v>0.95833333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="H24" s="22">
         <v>70</v>
       </c>
       <c r="I24" s="22">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="J24" s="21">
-        <v>0.98571428571428577</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="K24" s="19">
         <v>1</v>
       </c>
       <c r="L24" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="23">
         <v>1200</v>
       </c>
       <c r="O24" s="19">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="P24" s="21">
-        <v>1.1425000000000001</v>
+        <v>1.1391666666666667</v>
       </c>
       <c r="Q24" s="23">
         <v>90</v>
       </c>
       <c r="R24" s="19">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="S24" s="21">
-        <v>1.0333333333333334</v>
+        <v>0.91111111111111109</v>
       </c>
       <c r="T24" s="24">
-        <v>6000000</v>
+        <v>4771800</v>
       </c>
       <c r="U24" s="24">
-        <v>7453900</v>
+        <v>6500000</v>
       </c>
       <c r="V24" s="25">
-        <f t="shared" si="0"/>
-        <v>1.2423166666666667</v>
+        <v>0.73412307692307688</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -2551,11 +2532,11 @@
       </c>
       <c r="C25" s="27">
         <f>SUM(C2:C24)</f>
-        <v>51080.360000000015</v>
+        <v>49055.470000000016</v>
       </c>
       <c r="D25" s="21">
-        <f t="shared" ref="D25" si="1">C25/B25</f>
-        <v>0.91788607367475317</v>
+        <f t="shared" ref="D25" si="0">C25/B25</f>
+        <v>0.88149991015274065</v>
       </c>
       <c r="E25" s="26">
         <f>SUM(E2:E24)</f>
@@ -2563,11 +2544,11 @@
       </c>
       <c r="F25" s="26">
         <f>SUM(F2:F24)</f>
-        <v>939</v>
+        <v>988</v>
       </c>
       <c r="G25" s="21">
         <f>F25/E25</f>
-        <v>1.0096774193548388</v>
+        <v>1.0623655913978494</v>
       </c>
       <c r="H25" s="27">
         <f>SUM(H2:H24)</f>
@@ -2575,31 +2556,31 @@
       </c>
       <c r="I25" s="27">
         <f>SUM(I2:I24)</f>
-        <v>1769</v>
+        <v>1580</v>
       </c>
       <c r="J25" s="21">
-        <f t="shared" ref="J25" si="2">I25/H25</f>
-        <v>1.0332943925233644</v>
+        <f t="shared" ref="J25" si="1">I25/H25</f>
+        <v>0.92289719626168221</v>
       </c>
       <c r="K25" s="26">
         <f>SUM(K2:K24)</f>
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L25" s="26">
         <f>SUM(L2:L24)</f>
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="M25" s="21">
-        <f t="shared" ref="M25" si="3">L25/K25</f>
-        <v>0.80769230769230771</v>
+        <f t="shared" ref="M25" si="2">L25/K25</f>
+        <v>0.95424836601307195</v>
       </c>
       <c r="N25" s="26">
         <f>SUM(N2:N24)</f>
-        <v>27700</v>
+        <v>25304</v>
       </c>
       <c r="O25" s="26">
         <f>SUM(O2:O24)</f>
-        <v>25068</v>
+        <v>23456</v>
       </c>
       <c r="P25" s="21">
         <v>0.93129963898916968</v>
@@ -2610,23 +2591,23 @@
       </c>
       <c r="R25" s="26">
         <f>SUM(R2:R24)</f>
-        <v>3374</v>
+        <v>3434</v>
       </c>
       <c r="S25" s="21">
-        <f t="shared" ref="S25" si="4">R25/Q25</f>
-        <v>1.0365591397849463</v>
+        <f t="shared" ref="S25" si="3">R25/Q25</f>
+        <v>1.0549923195084485</v>
       </c>
       <c r="T25" s="28">
         <f>SUM(T2:T24)</f>
-        <v>117500000</v>
+        <v>100527506.15000004</v>
       </c>
       <c r="U25" s="28">
         <f>SUM(U2:U24)</f>
-        <v>107360604.15000001</v>
+        <v>120500000</v>
       </c>
       <c r="V25" s="25">
-        <f t="shared" ref="V25" si="5">U25/T25</f>
-        <v>0.91370726936170221</v>
+        <f t="shared" ref="V25" si="4">U25/T25</f>
+        <v>1.1986769056043072</v>
       </c>
     </row>
   </sheetData>
@@ -2659,62 +2640,60 @@
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S25 D2:D25 G2:G25 J2:J25 M2:M25 V2:V25 P2:P25">
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="between">
+  <conditionalFormatting sqref="P2:P24">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="greaterThan">
+      <formula>0.99</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="between">
+      <formula>0.9</formula>
+      <formula>0.99</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S25 P2:P25 D2:D25 G2:G25 J2:J25 M2:M25 V2:V25">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="between">
       <formula>0.8</formula>
       <formula>0.88</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S25">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="between">
       <formula>0.79</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="between">
       <formula>"79.9%"</formula>
       <formula>"89.9%"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="between">
       <formula>0.8</formula>
       <formula>0.89</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="between">
       <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S22">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="lessThan">
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V25">
-    <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="13" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="between">
       <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="greaterThan">
       <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P24">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>0.9</formula>
-      <formula>0.99</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P24">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/general.xlsx
+++ b/data/general.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/07 Julio/Dasboatdde junio/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/08 Agosto/Dasboatdde julio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A46F1B3-48BF-4027-BAE1-803F1E397436}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE8D7761-E8DB-4812-8D41-F62C68746562}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F008453E-1A06-40CE-9AA2-8079F823278A}"/>
   </bookViews>
@@ -266,7 +266,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -342,6 +342,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -966,64 +969,64 @@
         <v>2400</v>
       </c>
       <c r="C2" s="20">
-        <v>2781.8900000000008</v>
+        <v>2185.54</v>
       </c>
       <c r="D2" s="21">
-        <v>1.1591208333333336</v>
+        <v>0.91064166666666668</v>
       </c>
       <c r="E2" s="19">
         <v>30</v>
       </c>
       <c r="F2" s="19">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" s="21">
-        <v>1.1000000000000001</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="H2" s="22">
         <v>72</v>
       </c>
       <c r="I2" s="22">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="J2" s="21">
-        <v>1.2083333333333333</v>
+        <v>0.93055555555555558</v>
       </c>
       <c r="K2" s="19">
         <v>10</v>
       </c>
       <c r="L2" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M2" s="21">
-        <v>0.7</v>
-      </c>
-      <c r="N2" s="23">
+        <v>0.6</v>
+      </c>
+      <c r="N2" s="29">
         <v>1500</v>
       </c>
       <c r="O2" s="19">
-        <v>1616</v>
+        <v>1586</v>
       </c>
       <c r="P2" s="21">
-        <v>1.0773333333333333</v>
+        <v>1.0573333333333332</v>
       </c>
       <c r="Q2" s="23">
         <v>95</v>
       </c>
       <c r="R2" s="19">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="S2" s="21">
-        <v>1.5263157894736843</v>
+        <v>1.4105263157894736</v>
       </c>
       <c r="T2" s="24">
-        <v>9515700</v>
+        <v>9000000</v>
       </c>
       <c r="U2" s="24">
-        <v>9000000</v>
+        <v>6603800</v>
       </c>
       <c r="V2" s="25">
-        <v>1.0572999999999999</v>
+        <v>0.73375555555555561</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1034,64 +1037,64 @@
         <v>2850</v>
       </c>
       <c r="C3" s="20">
-        <v>2489.9300000000003</v>
+        <v>2754.5499999999993</v>
       </c>
       <c r="D3" s="21">
-        <v>0.87365964912280714</v>
+        <v>0.96650877192982432</v>
       </c>
       <c r="E3" s="19">
         <v>55</v>
       </c>
       <c r="F3" s="19">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G3" s="21">
-        <v>1.1090909090909091</v>
+        <v>1.509090909090909</v>
       </c>
       <c r="H3" s="22">
         <v>80</v>
       </c>
       <c r="I3" s="22">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="J3" s="21">
-        <v>0.85</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="K3" s="19">
         <v>14</v>
       </c>
       <c r="L3" s="19">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M3" s="21">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="N3" s="23">
-        <v>848</v>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="N3" s="29">
+        <v>1500</v>
       </c>
       <c r="O3" s="19">
-        <v>961</v>
+        <v>1537</v>
       </c>
       <c r="P3" s="21">
-        <v>1.133254716981132</v>
+        <v>1.0246666666666666</v>
       </c>
       <c r="Q3" s="23">
         <v>150</v>
       </c>
       <c r="R3" s="19">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="S3" s="21">
-        <v>1</v>
+        <v>1.1066666666666667</v>
       </c>
       <c r="T3" s="24">
-        <v>3183000</v>
+        <v>4000000</v>
       </c>
       <c r="U3" s="24">
-        <v>4500000</v>
+        <v>2339000</v>
       </c>
       <c r="V3" s="25">
-        <v>0.70733333333333337</v>
+        <v>0.58474999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -1102,64 +1105,64 @@
         <v>3700</v>
       </c>
       <c r="C4" s="20">
-        <v>3472.6200000000035</v>
+        <v>3099.9600000000041</v>
       </c>
       <c r="D4" s="21">
-        <v>0.93854594594594687</v>
+        <v>0.83782702702702816</v>
       </c>
       <c r="E4" s="19">
         <v>70</v>
       </c>
       <c r="F4" s="19">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="G4" s="21">
-        <v>0.81428571428571428</v>
+        <v>1.1857142857142857</v>
       </c>
       <c r="H4" s="22">
         <v>125</v>
       </c>
       <c r="I4" s="22">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="J4" s="21">
-        <v>0.96</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="K4" s="19">
         <v>10</v>
       </c>
       <c r="L4" s="19">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M4" s="21">
-        <v>1.9</v>
-      </c>
-      <c r="N4" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="N4" s="29">
         <v>1500</v>
       </c>
       <c r="O4" s="19">
-        <v>1523</v>
+        <v>1530</v>
       </c>
       <c r="P4" s="21">
-        <v>1.0153333333333334</v>
+        <v>1.02</v>
       </c>
       <c r="Q4" s="23">
         <v>220</v>
       </c>
       <c r="R4" s="19">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="S4" s="21">
-        <v>1.1136363636363635</v>
+        <v>1.2</v>
       </c>
       <c r="T4" s="24">
-        <v>8470815.2300000004</v>
+        <v>9000000</v>
       </c>
       <c r="U4" s="24">
-        <v>9500000</v>
+        <v>9076000</v>
       </c>
       <c r="V4" s="25">
-        <v>0.89166476105263159</v>
+        <v>1.0084444444444445</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1170,39 +1173,39 @@
         <v>1000</v>
       </c>
       <c r="C5" s="20">
-        <v>611.49000000000012</v>
+        <v>623.91999999999985</v>
       </c>
       <c r="D5" s="21">
-        <v>0.61149000000000009</v>
+        <v>0.62391999999999981</v>
       </c>
       <c r="E5" s="19">
         <v>8</v>
       </c>
       <c r="F5" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G5" s="21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="22">
         <v>40</v>
       </c>
       <c r="I5" s="22">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J5" s="21">
-        <v>0.75</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="K5" s="19">
         <v>2</v>
       </c>
       <c r="L5" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="N5" s="23">
+        <v>0</v>
+      </c>
+      <c r="N5" s="29">
         <v>0</v>
       </c>
       <c r="O5" s="19">
@@ -1215,19 +1218,19 @@
         <v>25</v>
       </c>
       <c r="R5" s="19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="S5" s="21">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="T5" s="24">
-        <v>1386900</v>
+        <v>2500000</v>
       </c>
       <c r="U5" s="24">
-        <v>2500000</v>
+        <v>1195000</v>
       </c>
       <c r="V5" s="25">
-        <v>0.55476000000000003</v>
+        <v>0.47799999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1238,28 +1241,28 @@
         <v>1500</v>
       </c>
       <c r="C6" s="20">
-        <v>1145.6399999999999</v>
+        <v>1367.2599999999993</v>
       </c>
       <c r="D6" s="21">
-        <v>0.76375999999999988</v>
+        <v>0.91150666666666624</v>
       </c>
       <c r="E6" s="19">
         <v>25</v>
       </c>
       <c r="F6" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="21">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="H6" s="22">
         <v>50</v>
       </c>
       <c r="I6" s="22">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J6" s="21">
-        <v>0.78</v>
+        <v>1.06</v>
       </c>
       <c r="K6" s="19">
         <v>1</v>
@@ -1270,32 +1273,32 @@
       <c r="M6" s="21">
         <v>0</v>
       </c>
-      <c r="N6" s="23">
-        <v>1200</v>
+      <c r="N6" s="29">
+        <v>800</v>
       </c>
       <c r="O6" s="19">
-        <v>1058</v>
+        <v>965</v>
       </c>
       <c r="P6" s="21">
-        <v>0.88166666666666671</v>
+        <v>1.20625</v>
       </c>
       <c r="Q6" s="23">
         <v>135</v>
       </c>
       <c r="R6" s="19">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="S6" s="21">
-        <v>1.1333333333333333</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="T6" s="24">
-        <v>4421900</v>
+        <v>6000000</v>
       </c>
       <c r="U6" s="24">
-        <v>5500000</v>
+        <v>3385700</v>
       </c>
       <c r="V6" s="25">
-        <v>0.80398181818181813</v>
+        <v>0.56428333333333336</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1306,64 +1309,64 @@
         <v>3000</v>
       </c>
       <c r="C7" s="20">
-        <v>3341.1700000000005</v>
+        <v>2611.3700000000003</v>
       </c>
       <c r="D7" s="21">
-        <v>1.1137233333333334</v>
+        <v>0.87045666666666677</v>
       </c>
       <c r="E7" s="19">
         <v>55</v>
       </c>
       <c r="F7" s="19">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G7" s="21">
-        <v>0.98181818181818181</v>
+        <v>0.8</v>
       </c>
       <c r="H7" s="22">
         <v>95</v>
       </c>
       <c r="I7" s="22">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="J7" s="21">
-        <v>1.0210526315789474</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="K7" s="19">
         <v>14</v>
       </c>
       <c r="L7" s="19">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M7" s="21">
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="N7" s="23">
-        <v>848</v>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="N7" s="29">
+        <v>1500</v>
       </c>
       <c r="O7" s="19">
-        <v>1273</v>
+        <v>1590</v>
       </c>
       <c r="P7" s="21">
-        <v>1.5011792452830188</v>
+        <v>1.06</v>
       </c>
       <c r="Q7" s="23">
         <v>180</v>
       </c>
       <c r="R7" s="19">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="S7" s="21">
-        <v>1</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="T7" s="24">
-        <v>10228200.079999998</v>
+        <v>8500000</v>
       </c>
       <c r="U7" s="24">
-        <v>8000000</v>
+        <v>9680800</v>
       </c>
       <c r="V7" s="25">
-        <v>1.2785250099999999</v>
+        <v>1.1389176470588236</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1374,28 +1377,28 @@
         <v>1450</v>
       </c>
       <c r="C8" s="20">
-        <v>940.4799999999999</v>
+        <v>803.4</v>
       </c>
       <c r="D8" s="21">
-        <v>0.6486068965517241</v>
+        <v>0.55406896551724139</v>
       </c>
       <c r="E8" s="19">
         <v>15</v>
       </c>
       <c r="F8" s="19">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8" s="21">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="H8" s="22">
         <v>50</v>
       </c>
       <c r="I8" s="22">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J8" s="21">
-        <v>0.74</v>
+        <v>0.6</v>
       </c>
       <c r="K8" s="19">
         <v>1</v>
@@ -1406,32 +1409,32 @@
       <c r="M8" s="21">
         <v>0</v>
       </c>
-      <c r="N8" s="23">
-        <v>417</v>
+      <c r="N8" s="29">
+        <v>1200</v>
       </c>
       <c r="O8" s="19">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="P8" s="21">
-        <v>0.88968824940047964</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="23">
         <v>60</v>
       </c>
       <c r="R8" s="19">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="S8" s="21">
-        <v>1.3</v>
+        <v>1.2333333333333334</v>
       </c>
       <c r="T8" s="24">
-        <v>1398000</v>
+        <v>3000000</v>
       </c>
       <c r="U8" s="24">
-        <v>3000000</v>
+        <v>1771000</v>
       </c>
       <c r="V8" s="25">
-        <v>0.46600000000000003</v>
+        <v>0.59033333333333338</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -1442,64 +1445,64 @@
         <v>1500</v>
       </c>
       <c r="C9" s="20">
-        <v>1084.3</v>
+        <v>998.18000000000006</v>
       </c>
       <c r="D9" s="21">
-        <v>0.72286666666666666</v>
+        <v>0.66545333333333334</v>
       </c>
       <c r="E9" s="19">
         <v>37</v>
       </c>
       <c r="F9" s="19">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G9" s="21">
-        <v>0.89189189189189189</v>
+        <v>0.67567567567567566</v>
       </c>
       <c r="H9" s="22">
         <v>45</v>
       </c>
       <c r="I9" s="22">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J9" s="21">
-        <v>0.73333333333333328</v>
+        <v>0.57777777777777772</v>
       </c>
       <c r="K9" s="19">
         <v>1</v>
       </c>
       <c r="L9" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="21">
-        <v>2</v>
-      </c>
-      <c r="N9" s="23">
+        <v>1</v>
+      </c>
+      <c r="N9" s="29">
         <v>1200</v>
       </c>
       <c r="O9" s="19">
-        <v>804</v>
+        <v>1228</v>
       </c>
       <c r="P9" s="21">
-        <v>0.67</v>
+        <v>1.0233333333333334</v>
       </c>
       <c r="Q9" s="23">
         <v>80</v>
       </c>
       <c r="R9" s="19">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="S9" s="21">
-        <v>1.0874999999999999</v>
+        <v>1.2875000000000001</v>
       </c>
       <c r="T9" s="24">
-        <v>3948900</v>
+        <v>5500000</v>
       </c>
       <c r="U9" s="24">
-        <v>5500000</v>
+        <v>3260000</v>
       </c>
       <c r="V9" s="25">
-        <v>0.71798181818181817</v>
+        <v>0.59272727272727277</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1510,64 +1513,64 @@
         <v>4000</v>
       </c>
       <c r="C10" s="20">
-        <v>3196.6400000000035</v>
+        <v>2731.7499999999995</v>
       </c>
       <c r="D10" s="21">
-        <v>0.79916000000000087</v>
+        <v>0.68293749999999986</v>
       </c>
       <c r="E10" s="19">
         <v>50</v>
       </c>
       <c r="F10" s="19">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="G10" s="21">
-        <v>1.56</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H10" s="22">
         <v>130</v>
       </c>
       <c r="I10" s="22">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="J10" s="21">
-        <v>0.86923076923076925</v>
+        <v>0.74615384615384617</v>
       </c>
       <c r="K10" s="19">
         <v>1</v>
       </c>
       <c r="L10" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="21">
-        <v>1</v>
-      </c>
-      <c r="N10" s="23">
+        <v>0</v>
+      </c>
+      <c r="N10" s="29">
         <v>1500</v>
       </c>
       <c r="O10" s="19">
-        <v>1263</v>
+        <v>886</v>
       </c>
       <c r="P10" s="21">
-        <v>0.84199999999999997</v>
+        <v>0.59066666666666667</v>
       </c>
       <c r="Q10" s="23">
         <v>180</v>
       </c>
       <c r="R10" s="19">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="S10" s="21">
-        <v>1.1666666666666667</v>
+        <v>1.211111111111111</v>
       </c>
       <c r="T10" s="24">
-        <v>5826700</v>
+        <v>7500000</v>
       </c>
       <c r="U10" s="24">
-        <v>7500000</v>
+        <v>5468000</v>
       </c>
       <c r="V10" s="25">
-        <v>0.77689333333333332</v>
+        <v>0.72906666666666664</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1578,64 +1581,64 @@
         <v>3500</v>
       </c>
       <c r="C11" s="20">
-        <v>3222.8200000000033</v>
+        <v>3050.7700000000032</v>
       </c>
       <c r="D11" s="21">
-        <v>0.92080571428571523</v>
+        <v>0.87164857142857233</v>
       </c>
       <c r="E11" s="19">
         <v>80</v>
       </c>
       <c r="F11" s="19">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="G11" s="21">
-        <v>0.95</v>
+        <v>1.2875000000000001</v>
       </c>
       <c r="H11" s="22">
         <v>90</v>
       </c>
       <c r="I11" s="22">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="J11" s="21">
-        <v>0.9555555555555556</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="K11" s="19">
         <v>20</v>
       </c>
       <c r="L11" s="19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M11" s="21">
-        <v>0.85</v>
-      </c>
-      <c r="N11" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="N11" s="29">
         <v>1500</v>
       </c>
       <c r="O11" s="19">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="P11" s="21">
-        <v>1.01</v>
+        <v>1.008</v>
       </c>
       <c r="Q11" s="23">
         <v>190</v>
       </c>
       <c r="R11" s="19">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="S11" s="21">
-        <v>1.168421052631579</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="T11" s="24">
-        <v>3107000</v>
+        <v>4500000</v>
       </c>
       <c r="U11" s="24">
-        <v>4500000</v>
+        <v>2969000</v>
       </c>
       <c r="V11" s="25">
-        <v>0.69044444444444442</v>
+        <v>0.6597777777777778</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1646,28 +1649,28 @@
         <v>2400</v>
       </c>
       <c r="C12" s="20">
-        <v>2358.04</v>
+        <v>2164.4100000000008</v>
       </c>
       <c r="D12" s="21">
-        <v>0.9825166666666667</v>
+        <v>0.90183750000000029</v>
       </c>
       <c r="E12" s="19">
         <v>24</v>
       </c>
       <c r="F12" s="19">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G12" s="21">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="H12" s="22">
         <v>110</v>
       </c>
       <c r="I12" s="22">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="J12" s="21">
-        <v>0.95454545454545459</v>
+        <v>0.88181818181818183</v>
       </c>
       <c r="K12" s="19">
         <v>1</v>
@@ -1678,32 +1681,32 @@
       <c r="M12" s="21">
         <v>0</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="29">
         <v>1500</v>
       </c>
       <c r="O12" s="19">
-        <v>756</v>
+        <v>1269</v>
       </c>
       <c r="P12" s="21">
-        <v>0.504</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="Q12" s="23">
         <v>80</v>
       </c>
       <c r="R12" s="19">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="S12" s="21">
-        <v>0.96250000000000002</v>
+        <v>1.075</v>
       </c>
       <c r="T12" s="24">
-        <v>8615004.3800000008</v>
+        <v>8500000</v>
       </c>
       <c r="U12" s="24">
-        <v>8500000</v>
+        <v>6298200</v>
       </c>
       <c r="V12" s="25">
-        <v>1.0135299270588236</v>
+        <v>0.74096470588235297</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1714,64 +1717,64 @@
         <v>2000</v>
       </c>
       <c r="C13" s="20">
-        <v>1384.7</v>
+        <v>1909.69</v>
       </c>
       <c r="D13" s="21">
-        <v>0.69235000000000002</v>
+        <v>0.95484500000000005</v>
       </c>
       <c r="E13" s="19">
         <v>35</v>
       </c>
       <c r="F13" s="19">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="G13" s="21">
-        <v>0.82857142857142863</v>
+        <v>1.5428571428571429</v>
       </c>
       <c r="H13" s="22">
         <v>50</v>
       </c>
       <c r="I13" s="22">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J13" s="21">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="K13" s="19">
         <v>8</v>
       </c>
       <c r="L13" s="19">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M13" s="21">
-        <v>0.25</v>
-      </c>
-      <c r="N13" s="23">
+        <v>0.875</v>
+      </c>
+      <c r="N13" s="29">
         <v>1200</v>
       </c>
       <c r="O13" s="19">
-        <v>1188</v>
+        <v>1221</v>
       </c>
       <c r="P13" s="21">
-        <v>0.99</v>
+        <v>1.0175000000000001</v>
       </c>
       <c r="Q13" s="23">
         <v>130</v>
       </c>
       <c r="R13" s="19">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="S13" s="21">
-        <v>1.0384615384615385</v>
+        <v>1.3</v>
       </c>
       <c r="T13" s="24">
-        <v>5368500</v>
+        <v>5500000</v>
       </c>
       <c r="U13" s="24">
-        <v>5500000</v>
+        <v>5020000</v>
       </c>
       <c r="V13" s="25">
-        <v>0.97609090909090912</v>
+        <v>0.91272727272727272</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1782,28 +1785,28 @@
         <v>2500</v>
       </c>
       <c r="C14" s="20">
-        <v>2691.0300000000016</v>
+        <v>2393.3399999999997</v>
       </c>
       <c r="D14" s="21">
-        <v>1.0764120000000006</v>
+        <v>0.95733599999999985</v>
       </c>
       <c r="E14" s="19">
         <v>50</v>
       </c>
       <c r="F14" s="19">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G14" s="21">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="H14" s="22">
         <v>75</v>
       </c>
       <c r="I14" s="22">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J14" s="21">
-        <v>0.93333333333333335</v>
+        <v>0.85333333333333339</v>
       </c>
       <c r="K14" s="19">
         <v>12</v>
@@ -1814,32 +1817,32 @@
       <c r="M14" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="29">
         <v>1500</v>
       </c>
       <c r="O14" s="19">
-        <v>1491</v>
+        <v>1565</v>
       </c>
       <c r="P14" s="21">
-        <v>0.99399999999999999</v>
+        <v>1.0433333333333332</v>
       </c>
       <c r="Q14" s="23">
         <v>180</v>
       </c>
       <c r="R14" s="19">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="S14" s="21">
-        <v>1.0277777777777777</v>
+        <v>1.1944444444444444</v>
       </c>
       <c r="T14" s="24">
-        <v>1570000</v>
+        <v>3000000</v>
       </c>
       <c r="U14" s="24">
-        <v>3000000</v>
+        <v>1199900</v>
       </c>
       <c r="V14" s="25">
-        <v>0.52333333333333332</v>
+        <v>0.39996666666666669</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1850,64 +1853,64 @@
         <v>6800</v>
       </c>
       <c r="C15" s="20">
-        <v>7204.5600000000031</v>
+        <v>7049.8900000000058</v>
       </c>
       <c r="D15" s="21">
-        <v>1.0594941176470594</v>
+        <v>1.0367485294117655</v>
       </c>
       <c r="E15" s="19">
         <v>140</v>
       </c>
       <c r="F15" s="19">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="G15" s="21">
-        <v>1.1571428571428573</v>
+        <v>1.3285714285714285</v>
       </c>
       <c r="H15" s="22">
         <v>220</v>
       </c>
       <c r="I15" s="22">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="J15" s="21">
-        <v>1.0681818181818181</v>
+        <v>0.94090909090909092</v>
       </c>
       <c r="K15" s="19">
         <v>14</v>
       </c>
       <c r="L15" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M15" s="21">
-        <v>1.0714285714285714</v>
-      </c>
-      <c r="N15" s="23">
+        <v>1.2142857142857142</v>
+      </c>
+      <c r="N15" s="29">
         <v>1500</v>
       </c>
       <c r="O15" s="19">
-        <v>1786</v>
+        <v>1582</v>
       </c>
       <c r="P15" s="21">
-        <v>1.1906666666666668</v>
+        <v>1.0546666666666666</v>
       </c>
       <c r="Q15" s="23">
         <v>450</v>
       </c>
       <c r="R15" s="19">
-        <v>452</v>
+        <v>608</v>
       </c>
       <c r="S15" s="21">
-        <v>1.0044444444444445</v>
+        <v>1.3511111111111112</v>
       </c>
       <c r="T15" s="24">
-        <v>8189563.1500000004</v>
+        <v>7500000</v>
       </c>
       <c r="U15" s="24">
-        <v>7000000</v>
+        <v>5659400</v>
       </c>
       <c r="V15" s="25">
-        <v>1.1699375928571429</v>
+        <v>0.75458666666666663</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1915,67 +1918,67 @@
         <v>25</v>
       </c>
       <c r="B16" s="19">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="C16" s="20">
-        <v>928.37999999999988</v>
+        <v>1206.5700000000006</v>
       </c>
       <c r="D16" s="21">
-        <v>0.61891999999999991</v>
+        <v>1.0054750000000006</v>
       </c>
       <c r="E16" s="19">
         <v>15</v>
       </c>
       <c r="F16" s="19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G16" s="21">
-        <v>1.2</v>
+        <v>1.4666666666666666</v>
       </c>
       <c r="H16" s="22">
         <v>30</v>
       </c>
       <c r="I16" s="22">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J16" s="21">
-        <v>0.8</v>
+        <v>1.0333333333333334</v>
       </c>
       <c r="K16" s="19">
         <v>8</v>
       </c>
       <c r="L16" s="19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M16" s="21">
-        <v>0.375</v>
-      </c>
-      <c r="N16" s="23">
+        <v>1</v>
+      </c>
+      <c r="N16" s="29">
         <v>1200</v>
       </c>
       <c r="O16" s="19">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="P16" s="21">
-        <v>1.0016666666666667</v>
+        <v>1.0041666666666667</v>
       </c>
       <c r="Q16" s="23">
         <v>70</v>
       </c>
       <c r="R16" s="19">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="S16" s="21">
-        <v>1.0142857142857142</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="T16" s="24">
-        <v>910897.93</v>
+        <v>2500000</v>
       </c>
       <c r="U16" s="24">
-        <v>2500000</v>
+        <v>1514000</v>
       </c>
       <c r="V16" s="25">
-        <v>0.36435917200000001</v>
+        <v>0.60560000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -1986,64 +1989,64 @@
         <v>2000</v>
       </c>
       <c r="C17" s="20">
-        <v>1478.3299999999992</v>
+        <v>1839.5399999999995</v>
       </c>
       <c r="D17" s="21">
-        <v>0.73916499999999963</v>
+        <v>0.91976999999999975</v>
       </c>
       <c r="E17" s="19">
         <v>15</v>
       </c>
       <c r="F17" s="19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G17" s="21">
-        <v>1.1333333333333333</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="H17" s="22">
         <v>75</v>
       </c>
       <c r="I17" s="22">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J17" s="21">
-        <v>0.7466666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="K17" s="19">
         <v>1</v>
       </c>
       <c r="L17" s="19">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M17" s="21">
-        <v>10</v>
-      </c>
-      <c r="N17" s="23">
-        <v>1200</v>
+        <v>3</v>
+      </c>
+      <c r="N17" s="29">
+        <v>800</v>
       </c>
       <c r="O17" s="19">
-        <v>1097</v>
+        <v>1009</v>
       </c>
       <c r="P17" s="21">
-        <v>0.91416666666666668</v>
+        <v>1.26125</v>
       </c>
       <c r="Q17" s="23">
         <v>70</v>
       </c>
       <c r="R17" s="19">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="S17" s="21">
-        <v>1.3571428571428572</v>
+        <v>1.0857142857142856</v>
       </c>
       <c r="T17" s="24">
-        <v>3376702.15</v>
+        <v>4500000</v>
       </c>
       <c r="U17" s="24">
-        <v>4500000</v>
+        <v>2940700</v>
       </c>
       <c r="V17" s="25">
-        <v>0.75037825555555548</v>
+        <v>0.6534888888888889</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -2054,64 +2057,64 @@
         <v>1100</v>
       </c>
       <c r="C18" s="20">
-        <v>1050.2500000000002</v>
+        <v>997.74</v>
       </c>
       <c r="D18" s="21">
-        <v>0.95477272727272744</v>
+        <v>0.90703636363636364</v>
       </c>
       <c r="E18" s="19">
         <v>20</v>
       </c>
       <c r="F18" s="19">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G18" s="21">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="H18" s="22">
         <v>30</v>
       </c>
       <c r="I18" s="22">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J18" s="21">
-        <v>1.2333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="K18" s="19">
         <v>4</v>
       </c>
       <c r="L18" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M18" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="N18" s="23">
-        <v>835</v>
+        <v>1</v>
+      </c>
+      <c r="N18" s="29">
+        <v>1200</v>
       </c>
       <c r="O18" s="19">
-        <v>594</v>
+        <v>1201</v>
       </c>
       <c r="P18" s="21">
-        <v>0.71137724550898207</v>
+        <v>1.0008333333333332</v>
       </c>
       <c r="Q18" s="23">
         <v>70</v>
       </c>
       <c r="R18" s="19">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="S18" s="21">
-        <v>1.2285714285714286</v>
+        <v>1.5142857142857142</v>
       </c>
       <c r="T18" s="24">
-        <v>1483002.15</v>
+        <v>2000000</v>
       </c>
       <c r="U18" s="24">
-        <v>2000000</v>
+        <v>1725000</v>
       </c>
       <c r="V18" s="25">
-        <v>0.74150107499999995</v>
+        <v>0.86250000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -2122,64 +2125,64 @@
         <v>2600</v>
       </c>
       <c r="C19" s="20">
-        <v>2194.4999999999986</v>
+        <v>2322.5700000000002</v>
       </c>
       <c r="D19" s="21">
-        <v>0.84403846153846096</v>
+        <v>0.89329615384615391</v>
       </c>
       <c r="E19" s="19">
         <v>62</v>
       </c>
       <c r="F19" s="19">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="21">
-        <v>0.88709677419354838</v>
+        <v>0.90322580645161288</v>
       </c>
       <c r="H19" s="22">
         <v>60</v>
       </c>
       <c r="I19" s="22">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J19" s="21">
-        <v>0.8666666666666667</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="K19" s="19">
         <v>14</v>
       </c>
       <c r="L19" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M19" s="21">
-        <v>1</v>
-      </c>
-      <c r="N19" s="23">
-        <v>913</v>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="N19" s="29">
+        <v>1500</v>
       </c>
       <c r="O19" s="19">
-        <v>487</v>
+        <v>1253</v>
       </c>
       <c r="P19" s="21">
-        <v>0.53340635268346115</v>
+        <v>0.83533333333333337</v>
       </c>
       <c r="Q19" s="23">
         <v>210</v>
       </c>
       <c r="R19" s="19">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="S19" s="21">
-        <v>0.85238095238095235</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="T19" s="24">
-        <v>1939902.15</v>
+        <v>4000000</v>
       </c>
       <c r="U19" s="24">
-        <v>4000000</v>
+        <v>3458700</v>
       </c>
       <c r="V19" s="25">
-        <v>0.4849755375</v>
+        <v>0.86467499999999997</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -2190,39 +2193,39 @@
         <v>1000</v>
       </c>
       <c r="C20" s="20">
-        <v>761.31999999999982</v>
+        <v>890.39000000000021</v>
       </c>
       <c r="D20" s="21">
-        <v>0.76131999999999977</v>
+        <v>0.89039000000000024</v>
       </c>
       <c r="E20" s="19">
         <v>15</v>
       </c>
       <c r="F20" s="19">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G20" s="21">
-        <v>1.1333333333333333</v>
+        <v>1.8</v>
       </c>
       <c r="H20" s="22">
         <v>30</v>
       </c>
       <c r="I20" s="22">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J20" s="21">
-        <v>0.9</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="K20" s="19">
         <v>4</v>
       </c>
       <c r="L20" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="21">
-        <v>0.25</v>
-      </c>
-      <c r="N20" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="N20" s="29">
         <v>0</v>
       </c>
       <c r="O20" s="19">
@@ -2235,19 +2238,19 @@
         <v>70</v>
       </c>
       <c r="R20" s="19">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="S20" s="21">
-        <v>0.82857142857142863</v>
+        <v>1</v>
       </c>
       <c r="T20" s="24">
-        <v>1684550</v>
+        <v>2500000</v>
       </c>
       <c r="U20" s="24">
-        <v>2500000</v>
+        <v>2267000</v>
       </c>
       <c r="V20" s="25">
-        <v>0.67381999999999997</v>
+        <v>0.90680000000000005</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -2258,28 +2261,28 @@
         <v>2200</v>
       </c>
       <c r="C21" s="20">
-        <v>2372.1799999999998</v>
+        <v>1896.9399999999991</v>
       </c>
       <c r="D21" s="21">
-        <v>1.0782636363636362</v>
+        <v>0.8622454545454542</v>
       </c>
       <c r="E21" s="19">
         <v>40</v>
       </c>
       <c r="F21" s="19">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G21" s="21">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="H21" s="22">
         <v>60</v>
       </c>
       <c r="I21" s="22">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="J21" s="21">
-        <v>0.98333333333333328</v>
+        <v>0.78333333333333333</v>
       </c>
       <c r="K21" s="19">
         <v>1</v>
@@ -2290,32 +2293,32 @@
       <c r="M21" s="21">
         <v>0</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="29">
         <v>1200</v>
       </c>
       <c r="O21" s="19">
-        <v>839</v>
+        <v>773</v>
       </c>
       <c r="P21" s="21">
-        <v>0.69916666666666671</v>
+        <v>0.64416666666666667</v>
       </c>
       <c r="Q21" s="23">
         <v>220</v>
       </c>
       <c r="R21" s="19">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="S21" s="21">
-        <v>0.90454545454545454</v>
+        <v>1.0136363636363637</v>
       </c>
       <c r="T21" s="24">
-        <v>4621656</v>
+        <v>5500000</v>
       </c>
       <c r="U21" s="24">
-        <v>5500000</v>
+        <v>5159900</v>
       </c>
       <c r="V21" s="25">
-        <v>0.84030109090909089</v>
+        <v>0.93816363636363631</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
@@ -2326,10 +2329,10 @@
         <v>2650</v>
       </c>
       <c r="C22" s="20">
-        <v>2035.7799999999995</v>
+        <v>2188.2499999999995</v>
       </c>
       <c r="D22" s="21">
-        <v>0.76821886792452809</v>
+        <v>0.8257547169811319</v>
       </c>
       <c r="E22" s="19">
         <v>35</v>
@@ -2344,46 +2347,46 @@
         <v>70</v>
       </c>
       <c r="I22" s="22">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J22" s="21">
-        <v>1.0285714285714285</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="K22" s="19">
         <v>3</v>
       </c>
       <c r="L22" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="21">
-        <v>0</v>
-      </c>
-      <c r="N22" s="23">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N22" s="29">
         <v>1500</v>
       </c>
       <c r="O22" s="19">
-        <v>1434</v>
+        <v>360</v>
       </c>
       <c r="P22" s="21">
-        <v>0.95599999999999996</v>
+        <v>0.24</v>
       </c>
       <c r="Q22" s="23">
         <v>140</v>
       </c>
       <c r="R22" s="19">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="S22" s="21">
-        <v>1.0142857142857142</v>
+        <v>1.5214285714285714</v>
       </c>
       <c r="T22" s="24">
-        <v>4369512.93</v>
+        <v>5500000</v>
       </c>
       <c r="U22" s="24">
-        <v>5500000</v>
+        <v>4574298</v>
       </c>
       <c r="V22" s="25">
-        <v>0.79445689636363626</v>
+        <v>0.83169054545454546</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -2394,64 +2397,64 @@
         <v>1800</v>
       </c>
       <c r="C23" s="20">
-        <v>1038.83</v>
+        <v>1151.1699999999996</v>
       </c>
       <c r="D23" s="21">
-        <v>0.57712777777777768</v>
+        <v>0.63953888888888866</v>
       </c>
       <c r="E23" s="19">
         <v>30</v>
       </c>
       <c r="F23" s="19">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G23" s="21">
-        <v>0.6333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H23" s="22">
         <v>55</v>
       </c>
       <c r="I23" s="22">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J23" s="21">
-        <v>0.61818181818181817</v>
+        <v>0.6</v>
       </c>
       <c r="K23" s="19">
         <v>8</v>
       </c>
       <c r="L23" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23" s="21">
-        <v>0.625</v>
-      </c>
-      <c r="N23" s="23">
-        <v>1043</v>
+        <v>0.5</v>
+      </c>
+      <c r="N23" s="29">
+        <v>1200</v>
       </c>
       <c r="O23" s="19">
-        <v>831</v>
+        <v>427</v>
       </c>
       <c r="P23" s="21">
-        <v>0.79674017257909879</v>
+        <v>0.35583333333333333</v>
       </c>
       <c r="Q23" s="23">
         <v>160</v>
       </c>
       <c r="R23" s="19">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="S23" s="21">
-        <v>1.15625</v>
+        <v>1.2</v>
       </c>
       <c r="T23" s="24">
-        <v>2139300</v>
+        <v>3500000</v>
       </c>
       <c r="U23" s="24">
-        <v>4000000</v>
+        <v>2051900</v>
       </c>
       <c r="V23" s="25">
-        <v>0.53482499999999999</v>
+        <v>0.58625714285714281</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -2462,64 +2465,64 @@
         <v>2200</v>
       </c>
       <c r="C24" s="20">
-        <v>1270.5899999999997</v>
+        <v>1519.3099999999995</v>
       </c>
       <c r="D24" s="21">
-        <v>0.57754090909090894</v>
+        <v>0.69059545454545435</v>
       </c>
       <c r="E24" s="19">
         <v>24</v>
       </c>
       <c r="F24" s="19">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G24" s="21">
-        <v>0.5</v>
+        <v>1.0833333333333333</v>
       </c>
       <c r="H24" s="22">
         <v>70</v>
       </c>
       <c r="I24" s="22">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="J24" s="21">
-        <v>0.7857142857142857</v>
+        <v>0.68571428571428572</v>
       </c>
       <c r="K24" s="19">
         <v>1</v>
       </c>
       <c r="L24" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="21">
-        <v>0</v>
-      </c>
-      <c r="N24" s="23">
+        <v>1</v>
+      </c>
+      <c r="N24" s="29">
         <v>1200</v>
       </c>
       <c r="O24" s="19">
-        <v>1367</v>
+        <v>1133</v>
       </c>
       <c r="P24" s="21">
-        <v>1.1391666666666667</v>
+        <v>0.94416666666666671</v>
       </c>
       <c r="Q24" s="23">
         <v>90</v>
       </c>
       <c r="R24" s="19">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="S24" s="21">
-        <v>0.91111111111111109</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="T24" s="24">
-        <v>4771800</v>
+        <v>6500000</v>
       </c>
       <c r="U24" s="24">
-        <v>6500000</v>
+        <v>5887800</v>
       </c>
       <c r="V24" s="25">
-        <v>0.73412307692307688</v>
+        <v>0.90581538461538458</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -2528,15 +2531,15 @@
       </c>
       <c r="B25" s="26">
         <f>SUM(B2:B24)</f>
-        <v>55650</v>
+        <v>55350</v>
       </c>
       <c r="C25" s="27">
         <f>SUM(C2:C24)</f>
-        <v>49055.470000000016</v>
+        <v>47756.510000000009</v>
       </c>
       <c r="D25" s="21">
         <f t="shared" ref="D25" si="0">C25/B25</f>
-        <v>0.88149991015274065</v>
+        <v>0.86280957542908776</v>
       </c>
       <c r="E25" s="26">
         <f>SUM(E2:E24)</f>
@@ -2544,11 +2547,11 @@
       </c>
       <c r="F25" s="26">
         <f>SUM(F2:F24)</f>
-        <v>988</v>
+        <v>1112</v>
       </c>
       <c r="G25" s="21">
         <f>F25/E25</f>
-        <v>1.0623655913978494</v>
+        <v>1.1956989247311829</v>
       </c>
       <c r="H25" s="27">
         <f>SUM(H2:H24)</f>
@@ -2556,11 +2559,11 @@
       </c>
       <c r="I25" s="27">
         <f>SUM(I2:I24)</f>
-        <v>1580</v>
+        <v>1462</v>
       </c>
       <c r="J25" s="21">
         <f t="shared" ref="J25" si="1">I25/H25</f>
-        <v>0.92289719626168221</v>
+        <v>0.8539719626168224</v>
       </c>
       <c r="K25" s="26">
         <f>SUM(K2:K24)</f>
@@ -2568,19 +2571,19 @@
       </c>
       <c r="L25" s="26">
         <f>SUM(L2:L24)</f>
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="M25" s="21">
         <f t="shared" ref="M25" si="2">L25/K25</f>
-        <v>0.95424836601307195</v>
+        <v>0.86928104575163401</v>
       </c>
       <c r="N25" s="26">
         <f>SUM(N2:N24)</f>
-        <v>25304</v>
+        <v>27700</v>
       </c>
       <c r="O25" s="26">
         <f>SUM(O2:O24)</f>
-        <v>23456</v>
+        <v>23832</v>
       </c>
       <c r="P25" s="21">
         <v>0.93129963898916968</v>
@@ -2591,23 +2594,23 @@
       </c>
       <c r="R25" s="26">
         <f>SUM(R2:R24)</f>
-        <v>3434</v>
+        <v>3875</v>
       </c>
       <c r="S25" s="21">
         <f t="shared" ref="S25" si="3">R25/Q25</f>
-        <v>1.0549923195084485</v>
+        <v>1.1904761904761905</v>
       </c>
       <c r="T25" s="28">
         <f>SUM(T2:T24)</f>
-        <v>100527506.15000004</v>
+        <v>120500000</v>
       </c>
       <c r="U25" s="28">
         <f>SUM(U2:U24)</f>
-        <v>120500000</v>
+        <v>93505098</v>
       </c>
       <c r="V25" s="25">
         <f t="shared" ref="V25" si="4">U25/T25</f>
-        <v>1.1986769056043072</v>
+        <v>0.77597591701244817</v>
       </c>
     </row>
   </sheetData>

--- a/data/general.xlsx
+++ b/data/general.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/08 Agosto/Dasboatdde julio/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/09 Septiembre/Dasboatdde agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="342" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE8D7761-E8DB-4812-8D41-F62C68746562}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92A3F3B9-7CCA-4DF6-990C-E586C8B5B9CE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F008453E-1A06-40CE-9AA2-8079F823278A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>CVS</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>% puntos</t>
+  </si>
+  <si>
+    <t>Metro Est. San Antonio</t>
   </si>
 </sst>
 </file>
@@ -338,13 +341,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -353,7 +356,77 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -867,10 +940,10 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" style="1" customWidth="1"/>
@@ -889,7 +962,8 @@
     <col min="17" max="17" width="8.5703125" customWidth="1"/>
     <col min="18" max="18" width="9.85546875" customWidth="1"/>
     <col min="19" max="19" width="7.7109375" customWidth="1"/>
-    <col min="20" max="21" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -969,64 +1043,64 @@
         <v>2400</v>
       </c>
       <c r="C2" s="20">
-        <v>2185.54</v>
+        <v>2580.5400000000009</v>
       </c>
       <c r="D2" s="21">
-        <v>0.91064166666666668</v>
+        <v>1.0752250000000003</v>
       </c>
       <c r="E2" s="19">
         <v>30</v>
       </c>
       <c r="F2" s="19">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G2" s="21">
-        <v>1.0666666666666667</v>
+        <v>1.4666666666666666</v>
       </c>
       <c r="H2" s="22">
         <v>72</v>
       </c>
       <c r="I2" s="22">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J2" s="21">
-        <v>0.93055555555555558</v>
+        <v>0.98611111111111116</v>
       </c>
       <c r="K2" s="19">
         <v>10</v>
       </c>
       <c r="L2" s="19">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M2" s="21">
-        <v>0.6</v>
-      </c>
-      <c r="N2" s="29">
+        <v>1.3</v>
+      </c>
+      <c r="N2" s="27">
         <v>1500</v>
       </c>
       <c r="O2" s="19">
-        <v>1586</v>
+        <v>1573</v>
       </c>
       <c r="P2" s="21">
-        <v>1.0573333333333332</v>
+        <v>1.0486666666666666</v>
       </c>
       <c r="Q2" s="23">
         <v>95</v>
       </c>
       <c r="R2" s="19">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="S2" s="21">
-        <v>1.4105263157894736</v>
+        <v>1.168421052631579</v>
       </c>
       <c r="T2" s="24">
-        <v>9000000</v>
+        <v>8000000</v>
       </c>
       <c r="U2" s="24">
-        <v>6603800</v>
+        <v>9265349</v>
       </c>
       <c r="V2" s="25">
-        <v>0.73375555555555561</v>
+        <v>1.1581686250000001</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1037,64 +1111,64 @@
         <v>2850</v>
       </c>
       <c r="C3" s="20">
-        <v>2754.5499999999993</v>
+        <v>2583.15</v>
       </c>
       <c r="D3" s="21">
-        <v>0.96650877192982432</v>
+        <v>0.9063684210526316</v>
       </c>
       <c r="E3" s="19">
         <v>55</v>
       </c>
       <c r="F3" s="19">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G3" s="21">
-        <v>1.509090909090909</v>
+        <v>1.3090909090909091</v>
       </c>
       <c r="H3" s="22">
         <v>80</v>
       </c>
       <c r="I3" s="22">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J3" s="21">
-        <v>1.0249999999999999</v>
+        <v>0.91249999999999998</v>
       </c>
       <c r="K3" s="19">
         <v>14</v>
       </c>
       <c r="L3" s="19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M3" s="21">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="N3" s="29">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="N3" s="27">
         <v>1500</v>
       </c>
       <c r="O3" s="19">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="P3" s="21">
-        <v>1.0246666666666666</v>
+        <v>1.034</v>
       </c>
       <c r="Q3" s="23">
         <v>150</v>
       </c>
       <c r="R3" s="19">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="S3" s="21">
-        <v>1.1066666666666667</v>
+        <v>0.87333333333333329</v>
       </c>
       <c r="T3" s="24">
         <v>4000000</v>
       </c>
       <c r="U3" s="24">
-        <v>2339000</v>
+        <v>3560900</v>
       </c>
       <c r="V3" s="25">
-        <v>0.58474999999999999</v>
+        <v>0.89022500000000004</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -1105,64 +1179,64 @@
         <v>3700</v>
       </c>
       <c r="C4" s="20">
-        <v>3099.9600000000041</v>
+        <v>2742.1400000000021</v>
       </c>
       <c r="D4" s="21">
-        <v>0.83782702702702816</v>
+        <v>0.74111891891891946</v>
       </c>
       <c r="E4" s="19">
         <v>70</v>
       </c>
       <c r="F4" s="19">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="G4" s="21">
-        <v>1.1857142857142857</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="H4" s="22">
         <v>125</v>
       </c>
       <c r="I4" s="22">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="J4" s="21">
-        <v>0.83199999999999996</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="K4" s="19">
         <v>10</v>
       </c>
       <c r="L4" s="19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M4" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="N4" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="N4" s="27">
         <v>1500</v>
       </c>
       <c r="O4" s="19">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="P4" s="21">
-        <v>1.02</v>
+        <v>1.024</v>
       </c>
       <c r="Q4" s="23">
         <v>220</v>
       </c>
       <c r="R4" s="19">
-        <v>264</v>
+        <v>183</v>
       </c>
       <c r="S4" s="21">
-        <v>1.2</v>
+        <v>0.83181818181818179</v>
       </c>
       <c r="T4" s="24">
-        <v>9000000</v>
+        <v>9500000</v>
       </c>
       <c r="U4" s="24">
-        <v>9076000</v>
+        <v>5740799.9999999991</v>
       </c>
       <c r="V4" s="25">
-        <v>1.0084444444444445</v>
+        <v>0.60429473684210522</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1173,10 +1247,10 @@
         <v>1000</v>
       </c>
       <c r="C5" s="20">
-        <v>623.91999999999985</v>
+        <v>498.95000000000016</v>
       </c>
       <c r="D5" s="21">
-        <v>0.62391999999999981</v>
+        <v>0.49895000000000017</v>
       </c>
       <c r="E5" s="19">
         <v>8</v>
@@ -1191,10 +1265,10 @@
         <v>40</v>
       </c>
       <c r="I5" s="22">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J5" s="21">
-        <v>0.77500000000000002</v>
+        <v>0.625</v>
       </c>
       <c r="K5" s="19">
         <v>2</v>
@@ -1205,7 +1279,7 @@
       <c r="M5" s="21">
         <v>0</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="27">
         <v>0</v>
       </c>
       <c r="O5" s="19">
@@ -1218,19 +1292,19 @@
         <v>25</v>
       </c>
       <c r="R5" s="19">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="S5" s="21">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="T5" s="24">
         <v>2500000</v>
       </c>
       <c r="U5" s="24">
-        <v>1195000</v>
+        <v>1328000</v>
       </c>
       <c r="V5" s="25">
-        <v>0.47799999999999998</v>
+        <v>0.53120000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1241,10 +1315,10 @@
         <v>1500</v>
       </c>
       <c r="C6" s="20">
-        <v>1367.2599999999993</v>
+        <v>1492.1399999999994</v>
       </c>
       <c r="D6" s="21">
-        <v>0.91150666666666624</v>
+        <v>0.99475999999999964</v>
       </c>
       <c r="E6" s="19">
         <v>25</v>
@@ -1268,19 +1342,19 @@
         <v>1</v>
       </c>
       <c r="L6" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="21">
-        <v>0</v>
-      </c>
-      <c r="N6" s="29">
+        <v>1</v>
+      </c>
+      <c r="N6" s="27">
         <v>800</v>
       </c>
       <c r="O6" s="19">
-        <v>965</v>
+        <v>890</v>
       </c>
       <c r="P6" s="21">
-        <v>1.20625</v>
+        <v>1.1125</v>
       </c>
       <c r="Q6" s="23">
         <v>135</v>
@@ -1292,13 +1366,13 @@
         <v>1.0222222222222221</v>
       </c>
       <c r="T6" s="24">
-        <v>6000000</v>
+        <v>5500000</v>
       </c>
       <c r="U6" s="24">
-        <v>3385700</v>
+        <v>6007000</v>
       </c>
       <c r="V6" s="25">
-        <v>0.56428333333333336</v>
+        <v>1.0921818181818181</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1309,64 +1383,64 @@
         <v>3000</v>
       </c>
       <c r="C7" s="20">
-        <v>2611.3700000000003</v>
+        <v>2443.9100000000012</v>
       </c>
       <c r="D7" s="21">
-        <v>0.87045666666666677</v>
+        <v>0.81463666666666712</v>
       </c>
       <c r="E7" s="19">
         <v>55</v>
       </c>
       <c r="F7" s="19">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G7" s="21">
-        <v>0.8</v>
+        <v>0.98181818181818181</v>
       </c>
       <c r="H7" s="22">
         <v>95</v>
       </c>
       <c r="I7" s="22">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="J7" s="21">
-        <v>0.89473684210526316</v>
+        <v>0.74736842105263157</v>
       </c>
       <c r="K7" s="19">
         <v>14</v>
       </c>
       <c r="L7" s="19">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M7" s="21">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="N7" s="29">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="N7" s="27">
         <v>1500</v>
       </c>
       <c r="O7" s="19">
-        <v>1590</v>
+        <v>1560</v>
       </c>
       <c r="P7" s="21">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Q7" s="23">
         <v>180</v>
       </c>
       <c r="R7" s="19">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="S7" s="21">
-        <v>1.0222222222222221</v>
+        <v>0.93888888888888888</v>
       </c>
       <c r="T7" s="24">
-        <v>8500000</v>
+        <v>9000000</v>
       </c>
       <c r="U7" s="24">
-        <v>9680800</v>
+        <v>7170900</v>
       </c>
       <c r="V7" s="25">
-        <v>1.1389176470588236</v>
+        <v>0.79676666666666662</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1377,28 +1451,28 @@
         <v>1450</v>
       </c>
       <c r="C8" s="20">
-        <v>803.4</v>
+        <v>1336.4799999999998</v>
       </c>
       <c r="D8" s="21">
-        <v>0.55406896551724139</v>
+        <v>0.92171034482758607</v>
       </c>
       <c r="E8" s="19">
         <v>15</v>
       </c>
       <c r="F8" s="19">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G8" s="21">
-        <v>0.8666666666666667</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="H8" s="22">
         <v>50</v>
       </c>
       <c r="I8" s="22">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="J8" s="21">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
       <c r="K8" s="19">
         <v>1</v>
@@ -1409,32 +1483,32 @@
       <c r="M8" s="21">
         <v>0</v>
       </c>
-      <c r="N8" s="29">
+      <c r="N8" s="27">
         <v>1200</v>
       </c>
       <c r="O8" s="19">
-        <v>0</v>
+        <v>1146</v>
       </c>
       <c r="P8" s="21">
-        <v>0</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="Q8" s="23">
         <v>60</v>
       </c>
       <c r="R8" s="19">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="S8" s="21">
-        <v>1.2333333333333334</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="T8" s="24">
         <v>3000000</v>
       </c>
       <c r="U8" s="24">
-        <v>1771000</v>
+        <v>1723000</v>
       </c>
       <c r="V8" s="25">
-        <v>0.59033333333333338</v>
+        <v>0.57433333333333336</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -1445,64 +1519,64 @@
         <v>1500</v>
       </c>
       <c r="C9" s="20">
-        <v>998.18000000000006</v>
+        <v>1005.3999999999996</v>
       </c>
       <c r="D9" s="21">
-        <v>0.66545333333333334</v>
+        <v>0.67026666666666646</v>
       </c>
       <c r="E9" s="19">
         <v>37</v>
       </c>
       <c r="F9" s="19">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G9" s="21">
-        <v>0.67567567567567566</v>
+        <v>0.72972972972972971</v>
       </c>
       <c r="H9" s="22">
         <v>45</v>
       </c>
       <c r="I9" s="22">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J9" s="21">
-        <v>0.57777777777777772</v>
+        <v>0.71111111111111114</v>
       </c>
       <c r="K9" s="19">
         <v>1</v>
       </c>
       <c r="L9" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="21">
-        <v>1</v>
-      </c>
-      <c r="N9" s="29">
+        <v>2</v>
+      </c>
+      <c r="N9" s="27">
         <v>1200</v>
       </c>
       <c r="O9" s="19">
-        <v>1228</v>
+        <v>1181</v>
       </c>
       <c r="P9" s="21">
-        <v>1.0233333333333334</v>
+        <v>0.98416666666666663</v>
       </c>
       <c r="Q9" s="23">
         <v>80</v>
       </c>
       <c r="R9" s="19">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="S9" s="21">
-        <v>1.2875000000000001</v>
+        <v>1.075</v>
       </c>
       <c r="T9" s="24">
-        <v>5500000</v>
+        <v>5000000</v>
       </c>
       <c r="U9" s="24">
-        <v>3260000</v>
+        <v>4229133</v>
       </c>
       <c r="V9" s="25">
-        <v>0.59272727272727277</v>
+        <v>0.84582659999999998</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1510,67 +1584,67 @@
         <v>19</v>
       </c>
       <c r="B10" s="19">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="C10" s="20">
-        <v>2731.7499999999995</v>
+        <v>2313.5600000000009</v>
       </c>
       <c r="D10" s="21">
-        <v>0.68293749999999986</v>
+        <v>0.66101714285714308</v>
       </c>
       <c r="E10" s="19">
         <v>50</v>
       </c>
       <c r="F10" s="19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G10" s="21">
-        <v>1.1000000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="H10" s="22">
         <v>130</v>
       </c>
       <c r="I10" s="22">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="J10" s="21">
-        <v>0.74615384615384617</v>
+        <v>0.64615384615384619</v>
       </c>
       <c r="K10" s="19">
         <v>1</v>
       </c>
       <c r="L10" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="21">
-        <v>0</v>
-      </c>
-      <c r="N10" s="29">
+        <v>1</v>
+      </c>
+      <c r="N10" s="27">
         <v>1500</v>
       </c>
       <c r="O10" s="19">
-        <v>886</v>
+        <v>1114</v>
       </c>
       <c r="P10" s="21">
-        <v>0.59066666666666667</v>
+        <v>0.7426666666666667</v>
       </c>
       <c r="Q10" s="23">
         <v>180</v>
       </c>
       <c r="R10" s="19">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="S10" s="21">
-        <v>1.211111111111111</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="T10" s="24">
         <v>7500000</v>
       </c>
       <c r="U10" s="24">
-        <v>5468000</v>
+        <v>6835600</v>
       </c>
       <c r="V10" s="25">
-        <v>0.72906666666666664</v>
+        <v>0.9114133333333333</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1581,64 +1655,64 @@
         <v>3500</v>
       </c>
       <c r="C11" s="20">
-        <v>3050.7700000000032</v>
+        <v>2200.7799999999988</v>
       </c>
       <c r="D11" s="21">
-        <v>0.87164857142857233</v>
+        <v>0.62879428571428542</v>
       </c>
       <c r="E11" s="19">
         <v>80</v>
       </c>
       <c r="F11" s="19">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="G11" s="21">
-        <v>1.2875000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="H11" s="22">
         <v>90</v>
       </c>
       <c r="I11" s="22">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J11" s="21">
-        <v>0.75555555555555554</v>
+        <v>0.68888888888888888</v>
       </c>
       <c r="K11" s="19">
         <v>20</v>
       </c>
       <c r="L11" s="19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M11" s="21">
-        <v>0.8</v>
-      </c>
-      <c r="N11" s="29">
+        <v>0.45</v>
+      </c>
+      <c r="N11" s="27">
         <v>1500</v>
       </c>
       <c r="O11" s="19">
-        <v>1512</v>
+        <v>1211</v>
       </c>
       <c r="P11" s="21">
-        <v>1.008</v>
+        <v>0.80733333333333335</v>
       </c>
       <c r="Q11" s="23">
         <v>190</v>
       </c>
       <c r="R11" s="19">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="S11" s="21">
-        <v>1.263157894736842</v>
+        <v>0.75263157894736843</v>
       </c>
       <c r="T11" s="24">
         <v>4500000</v>
       </c>
       <c r="U11" s="24">
-        <v>2969000</v>
+        <v>2574000</v>
       </c>
       <c r="V11" s="25">
-        <v>0.6597777777777778</v>
+        <v>0.57199999999999995</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1649,19 +1723,19 @@
         <v>2400</v>
       </c>
       <c r="C12" s="20">
-        <v>2164.4100000000008</v>
+        <v>2152.67</v>
       </c>
       <c r="D12" s="21">
-        <v>0.90183750000000029</v>
+        <v>0.89694583333333333</v>
       </c>
       <c r="E12" s="19">
         <v>24</v>
       </c>
       <c r="F12" s="19">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G12" s="21">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="H12" s="22">
         <v>110</v>
@@ -1681,32 +1755,32 @@
       <c r="M12" s="21">
         <v>0</v>
       </c>
-      <c r="N12" s="29">
+      <c r="N12" s="27">
         <v>1500</v>
       </c>
       <c r="O12" s="19">
-        <v>1269</v>
+        <v>1340</v>
       </c>
       <c r="P12" s="21">
-        <v>0.84599999999999997</v>
+        <v>0.89333333333333331</v>
       </c>
       <c r="Q12" s="23">
         <v>80</v>
       </c>
       <c r="R12" s="19">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="S12" s="21">
-        <v>1.075</v>
+        <v>1.3125</v>
       </c>
       <c r="T12" s="24">
-        <v>8500000</v>
+        <v>8000000</v>
       </c>
       <c r="U12" s="24">
-        <v>6298200</v>
+        <v>6748300</v>
       </c>
       <c r="V12" s="25">
-        <v>0.74096470588235297</v>
+        <v>0.84353750000000005</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1717,28 +1791,28 @@
         <v>2000</v>
       </c>
       <c r="C13" s="20">
-        <v>1909.69</v>
+        <v>1761.5500000000004</v>
       </c>
       <c r="D13" s="21">
-        <v>0.95484500000000005</v>
+        <v>0.8807750000000002</v>
       </c>
       <c r="E13" s="19">
         <v>35</v>
       </c>
       <c r="F13" s="19">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="G13" s="21">
-        <v>1.5428571428571429</v>
+        <v>1.1142857142857143</v>
       </c>
       <c r="H13" s="22">
         <v>50</v>
       </c>
       <c r="I13" s="22">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J13" s="21">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="K13" s="19">
         <v>8</v>
@@ -1749,32 +1823,32 @@
       <c r="M13" s="21">
         <v>0.875</v>
       </c>
-      <c r="N13" s="29">
+      <c r="N13" s="27">
         <v>1200</v>
       </c>
       <c r="O13" s="19">
-        <v>1221</v>
+        <v>1102</v>
       </c>
       <c r="P13" s="21">
-        <v>1.0175000000000001</v>
+        <v>0.91833333333333333</v>
       </c>
       <c r="Q13" s="23">
         <v>130</v>
       </c>
       <c r="R13" s="19">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="S13" s="21">
-        <v>1.3</v>
+        <v>0.97692307692307689</v>
       </c>
       <c r="T13" s="24">
         <v>5500000</v>
       </c>
       <c r="U13" s="24">
-        <v>5020000</v>
+        <v>3531900</v>
       </c>
       <c r="V13" s="25">
-        <v>0.91272727272727272</v>
+        <v>0.64216363636363638</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1785,64 +1859,64 @@
         <v>2500</v>
       </c>
       <c r="C14" s="20">
-        <v>2393.3399999999997</v>
+        <v>2191.4500000000012</v>
       </c>
       <c r="D14" s="21">
-        <v>0.95733599999999985</v>
+        <v>0.87658000000000047</v>
       </c>
       <c r="E14" s="19">
         <v>50</v>
       </c>
       <c r="F14" s="19">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G14" s="21">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="H14" s="22">
         <v>75</v>
       </c>
       <c r="I14" s="22">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J14" s="21">
-        <v>0.85333333333333339</v>
+        <v>0.8</v>
       </c>
       <c r="K14" s="19">
         <v>12</v>
       </c>
       <c r="L14" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M14" s="21">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N14" s="29">
+        <v>0.75</v>
+      </c>
+      <c r="N14" s="27">
         <v>1500</v>
       </c>
       <c r="O14" s="19">
-        <v>1565</v>
+        <v>1430</v>
       </c>
       <c r="P14" s="21">
-        <v>1.0433333333333332</v>
+        <v>0.95333333333333337</v>
       </c>
       <c r="Q14" s="23">
         <v>180</v>
       </c>
       <c r="R14" s="19">
-        <v>215</v>
+        <v>138</v>
       </c>
       <c r="S14" s="21">
-        <v>1.1944444444444444</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="T14" s="24">
         <v>3000000</v>
       </c>
       <c r="U14" s="24">
-        <v>1199900</v>
+        <v>1174000</v>
       </c>
       <c r="V14" s="25">
-        <v>0.39996666666666669</v>
+        <v>0.39133333333333331</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1853,64 +1927,64 @@
         <v>6800</v>
       </c>
       <c r="C15" s="20">
-        <v>7049.8900000000058</v>
+        <v>6469.8200000000079</v>
       </c>
       <c r="D15" s="21">
-        <v>1.0367485294117655</v>
+        <v>0.95144411764705994</v>
       </c>
       <c r="E15" s="19">
         <v>140</v>
       </c>
       <c r="F15" s="19">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="G15" s="21">
-        <v>1.3285714285714285</v>
+        <v>1.2428571428571429</v>
       </c>
       <c r="H15" s="22">
         <v>220</v>
       </c>
       <c r="I15" s="22">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="J15" s="21">
-        <v>0.94090909090909092</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="K15" s="19">
         <v>14</v>
       </c>
       <c r="L15" s="19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M15" s="21">
-        <v>1.2142857142857142</v>
-      </c>
-      <c r="N15" s="29">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="N15" s="27">
         <v>1500</v>
       </c>
       <c r="O15" s="19">
-        <v>1582</v>
+        <v>1742</v>
       </c>
       <c r="P15" s="21">
-        <v>1.0546666666666666</v>
+        <v>1.1613333333333333</v>
       </c>
       <c r="Q15" s="23">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="R15" s="19">
-        <v>608</v>
+        <v>411</v>
       </c>
       <c r="S15" s="21">
-        <v>1.3511111111111112</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="T15" s="24">
-        <v>7500000</v>
+        <v>7000000</v>
       </c>
       <c r="U15" s="24">
-        <v>5659400</v>
+        <v>5857400</v>
       </c>
       <c r="V15" s="25">
-        <v>0.75458666666666663</v>
+        <v>0.83677142857142861</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1921,784 +1995,889 @@
         <v>1200</v>
       </c>
       <c r="C16" s="20">
-        <v>1206.5700000000006</v>
+        <v>1238.07</v>
       </c>
       <c r="D16" s="21">
-        <v>1.0054750000000006</v>
+        <v>1.031725</v>
       </c>
       <c r="E16" s="19">
         <v>15</v>
       </c>
       <c r="F16" s="19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G16" s="21">
-        <v>1.4666666666666666</v>
+        <v>1.8</v>
       </c>
       <c r="H16" s="22">
         <v>30</v>
       </c>
       <c r="I16" s="22">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J16" s="21">
-        <v>1.0333333333333334</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K16" s="19">
         <v>8</v>
       </c>
       <c r="L16" s="19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M16" s="21">
-        <v>1</v>
-      </c>
-      <c r="N16" s="29">
+        <v>1.125</v>
+      </c>
+      <c r="N16" s="27">
         <v>1200</v>
       </c>
       <c r="O16" s="19">
-        <v>1205</v>
+        <v>1048</v>
       </c>
       <c r="P16" s="21">
-        <v>1.0041666666666667</v>
+        <v>0.87333333333333329</v>
       </c>
       <c r="Q16" s="23">
         <v>70</v>
       </c>
       <c r="R16" s="19">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="S16" s="21">
-        <v>1.0714285714285714</v>
+        <v>0.61428571428571432</v>
       </c>
       <c r="T16" s="24">
         <v>2500000</v>
       </c>
       <c r="U16" s="24">
-        <v>1514000</v>
+        <v>1228000</v>
       </c>
       <c r="V16" s="25">
-        <v>0.60560000000000003</v>
+        <v>0.49120000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B17" s="19">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="C17" s="20">
-        <v>1839.5399999999995</v>
+        <v>239.10999999999999</v>
       </c>
       <c r="D17" s="21">
-        <v>0.91976999999999975</v>
+        <v>0</v>
       </c>
       <c r="E17" s="19">
         <v>15</v>
       </c>
       <c r="F17" s="19">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G17" s="21">
-        <v>1.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H17" s="22">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I17" s="22">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="J17" s="21">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="K17" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L17" s="19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" s="21">
-        <v>3</v>
-      </c>
-      <c r="N17" s="29">
-        <v>800</v>
+        <v>0</v>
+      </c>
+      <c r="N17" s="27">
+        <v>0</v>
       </c>
       <c r="O17" s="19">
-        <v>1009</v>
+        <v>0</v>
       </c>
       <c r="P17" s="21">
-        <v>1.26125</v>
-      </c>
-      <c r="Q17" s="23">
-        <v>70</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="23"/>
       <c r="R17" s="19">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="S17" s="21">
-        <v>1.0857142857142856</v>
+        <v>0</v>
       </c>
       <c r="T17" s="24">
-        <v>4500000</v>
+        <v>0</v>
       </c>
       <c r="U17" s="24">
-        <v>2940700</v>
+        <v>0</v>
       </c>
       <c r="V17" s="25">
-        <v>0.6534888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="19">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="C18" s="20">
-        <v>997.74</v>
+        <v>1374.9999999999998</v>
       </c>
       <c r="D18" s="21">
-        <v>0.90703636363636364</v>
+        <v>0.68749999999999989</v>
       </c>
       <c r="E18" s="19">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F18" s="19">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G18" s="21">
-        <v>1.35</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="H18" s="22">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="I18" s="22">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J18" s="21">
-        <v>0.8666666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="K18" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L18" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M18" s="21">
         <v>1</v>
       </c>
-      <c r="N18" s="29">
-        <v>1200</v>
+      <c r="N18" s="27">
+        <v>800</v>
       </c>
       <c r="O18" s="19">
-        <v>1201</v>
+        <v>850</v>
       </c>
       <c r="P18" s="21">
-        <v>1.0008333333333332</v>
+        <v>1.0625</v>
       </c>
       <c r="Q18" s="23">
         <v>70</v>
       </c>
       <c r="R18" s="19">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="S18" s="21">
-        <v>1.5142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="T18" s="24">
-        <v>2000000</v>
+        <v>4000000</v>
       </c>
       <c r="U18" s="24">
-        <v>1725000</v>
+        <v>3397800</v>
       </c>
       <c r="V18" s="25">
-        <v>0.86250000000000004</v>
+        <v>0.84945000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="19">
-        <v>2600</v>
+        <v>1100</v>
       </c>
       <c r="C19" s="20">
-        <v>2322.5700000000002</v>
+        <v>863.32</v>
       </c>
       <c r="D19" s="21">
-        <v>0.89329615384615391</v>
+        <v>0.78483636363636367</v>
       </c>
       <c r="E19" s="19">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F19" s="19">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="G19" s="21">
-        <v>0.90322580645161288</v>
+        <v>1.25</v>
       </c>
       <c r="H19" s="22">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I19" s="22">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="J19" s="21">
-        <v>0.93333333333333335</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="K19" s="19">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L19" s="19">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="M19" s="21">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="N19" s="29">
-        <v>1500</v>
+        <v>0.5</v>
+      </c>
+      <c r="N19" s="27">
+        <v>1200</v>
       </c>
       <c r="O19" s="19">
-        <v>1253</v>
+        <v>1273</v>
       </c>
       <c r="P19" s="21">
-        <v>0.83533333333333337</v>
+        <v>1.0608333333333333</v>
       </c>
       <c r="Q19" s="23">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="R19" s="19">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="S19" s="21">
-        <v>0.97142857142857142</v>
+        <v>0.95294117647058818</v>
       </c>
       <c r="T19" s="24">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="U19" s="24">
-        <v>3458700</v>
+        <v>1015000</v>
       </c>
       <c r="V19" s="25">
-        <v>0.86467499999999997</v>
+        <v>0.50749999999999995</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B20" s="19">
-        <v>1000</v>
+        <v>2600</v>
       </c>
       <c r="C20" s="20">
-        <v>890.39000000000021</v>
+        <v>1736.2199999999998</v>
       </c>
       <c r="D20" s="21">
-        <v>0.89039000000000024</v>
+        <v>0.66777692307692305</v>
       </c>
       <c r="E20" s="19">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F20" s="19">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="G20" s="21">
-        <v>1.8</v>
+        <v>0.88709677419354838</v>
       </c>
       <c r="H20" s="22">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I20" s="22">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J20" s="21">
-        <v>0.8666666666666667</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="K20" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L20" s="19">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M20" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="N20" s="29">
-        <v>0</v>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="N20" s="27">
+        <v>1500</v>
       </c>
       <c r="O20" s="19">
-        <v>0</v>
+        <v>1348</v>
       </c>
       <c r="P20" s="21">
-        <v>0</v>
+        <v>0.89866666666666661</v>
       </c>
       <c r="Q20" s="23">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="R20" s="19">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="S20" s="21">
-        <v>1</v>
+        <v>0.66190476190476188</v>
       </c>
       <c r="T20" s="24">
-        <v>2500000</v>
+        <v>4000000</v>
       </c>
       <c r="U20" s="24">
-        <v>2267000</v>
+        <v>2472700</v>
       </c>
       <c r="V20" s="25">
-        <v>0.90680000000000005</v>
+        <v>0.61817500000000003</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B21" s="19">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="C21" s="20">
-        <v>1896.9399999999991</v>
+        <v>1045.0899999999997</v>
       </c>
       <c r="D21" s="21">
-        <v>0.8622454545454542</v>
+        <v>1.0450899999999996</v>
       </c>
       <c r="E21" s="19">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F21" s="19">
+        <v>22</v>
+      </c>
+      <c r="G21" s="21">
+        <v>1.4666666666666666</v>
+      </c>
+      <c r="H21" s="22">
+        <v>30</v>
+      </c>
+      <c r="I21" s="22">
+        <v>31</v>
+      </c>
+      <c r="J21" s="21">
+        <v>1.0333333333333334</v>
+      </c>
+      <c r="K21" s="19">
+        <v>4</v>
+      </c>
+      <c r="L21" s="19">
+        <v>2</v>
+      </c>
+      <c r="M21" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="N21" s="27">
+        <v>0</v>
+      </c>
+      <c r="O21" s="19">
+        <v>0</v>
+      </c>
+      <c r="P21" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>70</v>
+      </c>
+      <c r="R21" s="19">
         <v>64</v>
       </c>
-      <c r="G21" s="21">
-        <v>1.6</v>
-      </c>
-      <c r="H21" s="22">
-        <v>60</v>
-      </c>
-      <c r="I21" s="22">
-        <v>47</v>
-      </c>
-      <c r="J21" s="21">
-        <v>0.78333333333333333</v>
-      </c>
-      <c r="K21" s="19">
-        <v>1</v>
-      </c>
-      <c r="L21" s="19">
-        <v>0</v>
-      </c>
-      <c r="M21" s="21">
-        <v>0</v>
-      </c>
-      <c r="N21" s="29">
-        <v>1200</v>
-      </c>
-      <c r="O21" s="19">
-        <v>773</v>
-      </c>
-      <c r="P21" s="21">
-        <v>0.64416666666666667</v>
-      </c>
-      <c r="Q21" s="23">
-        <v>220</v>
-      </c>
-      <c r="R21" s="19">
-        <v>223</v>
-      </c>
       <c r="S21" s="21">
-        <v>1.0136363636363637</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="T21" s="24">
-        <v>5500000</v>
+        <v>3000000</v>
       </c>
       <c r="U21" s="24">
-        <v>5159900</v>
+        <v>1422900</v>
       </c>
       <c r="V21" s="25">
-        <v>0.93816363636363631</v>
+        <v>0.4743</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="19">
-        <v>2650</v>
+        <v>2200</v>
       </c>
       <c r="C22" s="20">
-        <v>2188.2499999999995</v>
+        <v>1436.5899999999995</v>
       </c>
       <c r="D22" s="21">
-        <v>0.8257547169811319</v>
+        <v>0.65299545454545427</v>
       </c>
       <c r="E22" s="19">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F22" s="19">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G22" s="21">
-        <v>1.3714285714285714</v>
+        <v>1.375</v>
       </c>
       <c r="H22" s="22">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I22" s="22">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="J22" s="21">
-        <v>1.0714285714285714</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="K22" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" s="19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="21">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N22" s="29">
-        <v>1500</v>
+        <v>0</v>
+      </c>
+      <c r="N22" s="27">
+        <v>1200</v>
       </c>
       <c r="O22" s="19">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="P22" s="21">
-        <v>0.24</v>
+        <v>0.35833333333333334</v>
       </c>
       <c r="Q22" s="23">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="R22" s="19">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="S22" s="21">
-        <v>1.5214285714285714</v>
+        <v>0.98636363636363633</v>
       </c>
       <c r="T22" s="24">
-        <v>5500000</v>
+        <v>5000000</v>
       </c>
       <c r="U22" s="24">
-        <v>4574298</v>
+        <v>3033000</v>
       </c>
       <c r="V22" s="25">
-        <v>0.83169054545454546</v>
+        <v>0.60660000000000003</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="19">
-        <v>1800</v>
+        <v>2650</v>
       </c>
       <c r="C23" s="20">
-        <v>1151.1699999999996</v>
+        <v>1674.07</v>
       </c>
       <c r="D23" s="21">
-        <v>0.63953888888888866</v>
+        <v>0.63172452830188675</v>
       </c>
       <c r="E23" s="19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F23" s="19">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G23" s="21">
-        <v>1</v>
+        <v>0.94285714285714284</v>
       </c>
       <c r="H23" s="22">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I23" s="22">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J23" s="21">
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="K23" s="19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L23" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M23" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="N23" s="29">
-        <v>1200</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N23" s="27">
+        <v>1500</v>
       </c>
       <c r="O23" s="19">
-        <v>427</v>
+        <v>1513</v>
       </c>
       <c r="P23" s="21">
-        <v>0.35583333333333333</v>
+        <v>1.0086666666666666</v>
       </c>
       <c r="Q23" s="23">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="R23" s="19">
-        <v>192</v>
-      </c>
-      <c r="S23" s="21">
-        <v>1.2</v>
+        <v>115</v>
+      </c>
+      <c r="S23" s="28">
+        <v>0.63888888888888884</v>
       </c>
       <c r="T23" s="24">
-        <v>3500000</v>
+        <v>5500000</v>
       </c>
       <c r="U23" s="24">
-        <v>2051900</v>
+        <v>3662900</v>
       </c>
       <c r="V23" s="25">
-        <v>0.58625714285714281</v>
+        <v>0.66598181818181823</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="19">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="C24" s="20">
-        <v>1519.3099999999995</v>
+        <v>1190.7199999999996</v>
       </c>
       <c r="D24" s="21">
-        <v>0.69059545454545435</v>
+        <v>0.66151111111111083</v>
       </c>
       <c r="E24" s="19">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F24" s="19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G24" s="21">
-        <v>1.0833333333333333</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="H24" s="22">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I24" s="22">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J24" s="21">
-        <v>0.68571428571428572</v>
+        <v>0.65454545454545454</v>
       </c>
       <c r="K24" s="19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L24" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M24" s="21">
-        <v>1</v>
-      </c>
-      <c r="N24" s="29">
+        <v>0.875</v>
+      </c>
+      <c r="N24" s="27">
         <v>1200</v>
       </c>
       <c r="O24" s="19">
-        <v>1133</v>
+        <v>511</v>
       </c>
       <c r="P24" s="21">
-        <v>0.94416666666666671</v>
+        <v>0.42583333333333334</v>
       </c>
       <c r="Q24" s="23">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="R24" s="19">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="S24" s="21">
-        <v>1.0666666666666667</v>
+        <v>1.08125</v>
       </c>
       <c r="T24" s="24">
-        <v>6500000</v>
+        <v>3000000</v>
       </c>
       <c r="U24" s="24">
-        <v>5887800</v>
+        <v>1542000</v>
       </c>
       <c r="V24" s="25">
-        <v>0.90581538461538458</v>
+        <v>0.51400000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="19">
+        <v>1800</v>
+      </c>
+      <c r="C25" s="20">
+        <v>1266.2200000000003</v>
+      </c>
+      <c r="D25" s="21">
+        <v>0.70345555555555572</v>
+      </c>
+      <c r="E25" s="19">
+        <v>24</v>
+      </c>
+      <c r="F25" s="19">
+        <v>28</v>
+      </c>
+      <c r="G25" s="21">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="H25" s="22">
+        <v>70</v>
+      </c>
+      <c r="I25" s="22">
+        <v>34</v>
+      </c>
+      <c r="J25" s="21">
+        <v>0.48571428571428571</v>
+      </c>
+      <c r="K25" s="19">
+        <v>1</v>
+      </c>
+      <c r="L25" s="19">
+        <v>0</v>
+      </c>
+      <c r="M25" s="21">
+        <v>0</v>
+      </c>
+      <c r="N25" s="27">
+        <v>1200</v>
+      </c>
+      <c r="O25" s="19">
+        <v>1162</v>
+      </c>
+      <c r="P25" s="21">
+        <v>0.96833333333333338</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>90</v>
+      </c>
+      <c r="R25" s="19">
+        <v>52</v>
+      </c>
+      <c r="S25" s="21">
+        <v>0.57777777777777772</v>
+      </c>
+      <c r="T25" s="24">
+        <v>6000000</v>
+      </c>
+      <c r="U25" s="24">
+        <v>2957000</v>
+      </c>
+      <c r="V25" s="25">
+        <v>0.49283333333333335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="26">
-        <f>SUM(B2:B24)</f>
-        <v>55350</v>
-      </c>
-      <c r="C25" s="27">
-        <f>SUM(C2:C24)</f>
-        <v>47756.510000000009</v>
-      </c>
-      <c r="D25" s="21">
-        <f t="shared" ref="D25" si="0">C25/B25</f>
-        <v>0.86280957542908776</v>
-      </c>
-      <c r="E25" s="26">
-        <f>SUM(E2:E24)</f>
-        <v>930</v>
-      </c>
-      <c r="F25" s="26">
-        <f>SUM(F2:F24)</f>
-        <v>1112</v>
-      </c>
-      <c r="G25" s="21">
-        <f>F25/E25</f>
-        <v>1.1956989247311829</v>
-      </c>
-      <c r="H25" s="27">
-        <f>SUM(H2:H24)</f>
+      <c r="B26" s="29">
+        <f>SUM(B2:B25)</f>
+        <v>54450</v>
+      </c>
+      <c r="C26" s="29">
+        <f>SUM(C2:C25)</f>
+        <v>43836.950000000004</v>
+      </c>
+      <c r="D26" s="21">
+        <f>C26/B26</f>
+        <v>0.80508631772268147</v>
+      </c>
+      <c r="E26" s="29">
+        <f>SUM(E2:E25)</f>
+        <v>945</v>
+      </c>
+      <c r="F26" s="29">
+        <f>SUM(F2:F25)</f>
+        <v>1000</v>
+      </c>
+      <c r="G26" s="21">
+        <f>F26/E26</f>
+        <v>1.0582010582010581</v>
+      </c>
+      <c r="H26" s="29">
+        <f>SUM(H2:H25)</f>
         <v>1712</v>
       </c>
-      <c r="I25" s="27">
-        <f>SUM(I2:I24)</f>
-        <v>1462</v>
-      </c>
-      <c r="J25" s="21">
-        <f t="shared" ref="J25" si="1">I25/H25</f>
-        <v>0.8539719626168224</v>
-      </c>
-      <c r="K25" s="26">
-        <f>SUM(K2:K24)</f>
-        <v>153</v>
-      </c>
-      <c r="L25" s="26">
-        <f>SUM(L2:L24)</f>
-        <v>133</v>
-      </c>
-      <c r="M25" s="21">
-        <f t="shared" ref="M25" si="2">L25/K25</f>
-        <v>0.86928104575163401</v>
-      </c>
-      <c r="N25" s="26">
-        <f>SUM(N2:N24)</f>
+      <c r="I26" s="29">
+        <f>SUM(I2:I25)</f>
+        <v>1333</v>
+      </c>
+      <c r="J26" s="21">
+        <f>I26/H26</f>
+        <v>0.77862149532710279</v>
+      </c>
+      <c r="K26" s="29">
+        <f>SUM(K2:K25)</f>
+        <v>157</v>
+      </c>
+      <c r="L26" s="29">
+        <f>SUM(L2:L25)</f>
+        <v>125</v>
+      </c>
+      <c r="M26" s="21">
+        <f>L26/K26</f>
+        <v>0.79617834394904463</v>
+      </c>
+      <c r="N26" s="29">
+        <f>SUM(N2:N25)</f>
         <v>27700</v>
       </c>
-      <c r="O25" s="26">
-        <f>SUM(O2:O24)</f>
-        <v>23832</v>
-      </c>
-      <c r="P25" s="21">
-        <v>0.93129963898916968</v>
-      </c>
-      <c r="Q25" s="26">
-        <f>SUM(Q2:Q24)</f>
-        <v>3255</v>
-      </c>
-      <c r="R25" s="26">
-        <f>SUM(R2:R24)</f>
-        <v>3875</v>
-      </c>
-      <c r="S25" s="21">
-        <f t="shared" ref="S25" si="3">R25/Q25</f>
-        <v>1.1904761904761905</v>
-      </c>
-      <c r="T25" s="28">
-        <f>SUM(T2:T24)</f>
-        <v>120500000</v>
-      </c>
-      <c r="U25" s="28">
-        <f>SUM(U2:U24)</f>
-        <v>93505098</v>
-      </c>
-      <c r="V25" s="25">
-        <f t="shared" ref="V25" si="4">U25/T25</f>
-        <v>0.77597591701244817</v>
+      <c r="O26" s="29">
+        <f>SUM(O2:O25)</f>
+        <v>25511</v>
+      </c>
+      <c r="P26" s="21">
+        <f>O26/N26</f>
+        <v>0.92097472924187729</v>
+      </c>
+      <c r="Q26" s="29">
+        <f>SUM(Q2:Q25)</f>
+        <v>3360</v>
+      </c>
+      <c r="R26" s="29">
+        <f>SUM(R2:R25)</f>
+        <v>2975</v>
+      </c>
+      <c r="S26" s="21">
+        <f>R26/Q26</f>
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="T26" s="29">
+        <f>SUM(T2:T25)</f>
+        <v>117000000</v>
+      </c>
+      <c r="U26" s="29">
+        <f>SUM(U2:U25)</f>
+        <v>86477582</v>
+      </c>
+      <c r="V26" s="21">
+        <f>U26/T26</f>
+        <v>0.73912463247863247</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V24">
-    <sortCondition ref="A2:A24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V25">
+    <sortCondition ref="A2:A25"/>
   </sortState>
-  <conditionalFormatting sqref="D2:D25 G2:G25 J2:J25 M2:M25 S2:S25">
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="between">
+  <conditionalFormatting sqref="D2:D26 G2:G26 J2:J26 M2:M26 S2:S26">
+    <cfRule type="cellIs" dxfId="24" priority="23" operator="between">
       <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25 G2:G25">
-    <cfRule type="cellIs" dxfId="16" priority="19" operator="greaterThan">
+  <conditionalFormatting sqref="D2:D26 G2:G26">
+    <cfRule type="cellIs" dxfId="23" priority="26" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G25">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="18" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J25 M2:M25 P2:P25">
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="25" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M25">
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="22" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P24">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="P2:P25">
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="between">
       <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S25 P2:P25 D2:D25 G2:G25 J2:J25 M2:M25 V2:V25">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="between">
+  <conditionalFormatting sqref="D2:D26 G2:G26 J2:J26 M2:M26 P2:P26 S2:S26 V2:V26">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="between">
       <formula>0.8</formula>
       <formula>0.88</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S25">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="between">
       <formula>0.79</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="between">
       <formula>"79.9%"</formula>
       <formula>"89.9%"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="between">
       <formula>0.8</formula>
       <formula>0.89</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="between">
       <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="16" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="17" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S22">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="lessThan">
+  <conditionalFormatting sqref="S23">
+    <cfRule type="cellIs" dxfId="10" priority="15" operator="lessThan">
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V25">
-    <cfRule type="cellIs" dxfId="2" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="21" operator="between">
       <formula>0.9</formula>
       <formula>0.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="24" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P26">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="between">
+      <formula>0.9</formula>
+      <formula>0.99</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P26">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S26">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V26">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+      <formula>0.9</formula>
+      <formula>0.99</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V26">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>